--- a/media_references.xlsx
+++ b/media_references.xlsx
@@ -445,288 +445,288 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.54a7799.webp</v>
+        <v>/home/homeVideo.mov</v>
       </c>
       <c r="B5" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/Routes/landing.tsx</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.99dded0.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.54a7799.webp</v>
       </c>
       <c r="B6" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.6dced12.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.99dded0.webp</v>
       </c>
       <c r="B7" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.9d46069.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.6dced12.webp</v>
       </c>
       <c r="B8" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fit.47db4b5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.9d46069.webp</v>
       </c>
       <c r="B9" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C9">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wide.735b796.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/fit.47db4b5.webp</v>
       </c>
       <c r="B10" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C10">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.578008f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wide.735b796.webp</v>
       </c>
       <c r="B11" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.5f86ac3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.578008f.webp</v>
       </c>
       <c r="B12" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C12">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.083e652.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.5f86ac3.webp</v>
       </c>
       <c r="B13" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C13">
-        <v>64</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.07e7d88.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.083e652.webp</v>
       </c>
       <c r="B14" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C14">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/mass.bb8baa5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.07e7d88.webp</v>
       </c>
       <c r="B15" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C15">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/openWindow.5839f5b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/mass.bb8baa5.webp</v>
       </c>
       <c r="B16" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C16">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.f34a4ea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/openWindow.5839f5b.webp</v>
       </c>
       <c r="B17" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C17">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.975870d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.f34a4ea.webp</v>
       </c>
       <c r="B18" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C18">
-        <v>110</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wellness.bd707c7.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.975870d.webp</v>
       </c>
       <c r="B19" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C19">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.975870d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wellness.bd707c7.webp</v>
       </c>
       <c r="B20" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C20">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2L.91c45e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.975870d.webp</v>
       </c>
       <c r="B21" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C21">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/well.fcab3b9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2L.91c45e9.webp</v>
       </c>
       <c r="B22" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C22">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.1b81bb4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/well.fcab3b9.webp</v>
       </c>
       <c r="B23" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C23">
-        <v>155</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.02cca05.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.1b81bb4.webp</v>
       </c>
       <c r="B24" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C24">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.33fc8c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.02cca05.webp</v>
       </c>
       <c r="B25" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C25">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/5.f39e554.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.33fc8c3.webp</v>
       </c>
       <c r="B26" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C26">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/well2.82034ac.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/5.f39e554.webp</v>
       </c>
       <c r="B27" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C27">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long1.9fafbdc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/well2.82034ac.webp</v>
       </c>
       <c r="B28" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C28">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.5a8bb06.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long1.9fafbdc.webp</v>
       </c>
       <c r="B29" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C29">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterhouseLong.48262ff.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.5a8bb06.webp</v>
       </c>
       <c r="B30" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C30">
-        <v>14</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31">
@@ -737,315 +737,315 @@
         <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wavepoolLong.5549e3f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterhouseLong.48262ff.webp</v>
       </c>
       <c r="B32" t="str">
         <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SpiralSlideLong.9db3edb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wavepoolLong.5549e3f.webp</v>
       </c>
       <c r="B33" t="str">
         <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C33">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/boomLong.81f1304.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SpiralSlideLong.9db3edb.webp</v>
       </c>
       <c r="B34" t="str">
         <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C34">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/FikatCircusLong.c96ffbc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/boomLong.81f1304.webp</v>
       </c>
       <c r="B35" t="str">
         <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C35">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GiftshopLong.008270b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/FikatCircusLong.c96ffbc.webp</v>
       </c>
       <c r="B36" t="str">
         <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C36">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp1.d4c3656.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GiftshopLong.008270b.webp</v>
       </c>
       <c r="B37" t="str">
         <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C37">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp2.9bf24be.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/exp1.d4c3656.webp</v>
       </c>
       <c r="B38" t="str">
         <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C38">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp3.f02533c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/exp2.9bf24be.webp</v>
       </c>
       <c r="B39" t="str">
         <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C39">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.75aadd4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/exp3.f02533c.webp</v>
       </c>
       <c r="B40" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Glamping.75aadd4.webp</v>
       </c>
       <c r="B41" t="str">
         <v>src/MockData/room.tsx</v>
       </c>
       <c r="C41">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_spa1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
       </c>
       <c r="B42" t="str">
         <v>src/MockData/room.tsx</v>
       </c>
       <c r="C42">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_premium_suite.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_spa1.webp</v>
       </c>
       <c r="B43" t="str">
         <v>src/MockData/room.tsx</v>
       </c>
       <c r="C43">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_junior_suite.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_premium_suite.webp</v>
       </c>
       <c r="B44" t="str">
         <v>src/MockData/room.tsx</v>
       </c>
       <c r="C44">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_executive_suite.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_junior_suite.webp</v>
       </c>
       <c r="B45" t="str">
         <v>src/MockData/room.tsx</v>
       </c>
       <c r="C45">
-        <v>82</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_presidential_suite.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_executive_suite.webp</v>
       </c>
       <c r="B46" t="str">
         <v>src/MockData/room.tsx</v>
       </c>
       <c r="C46">
-        <v>109</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.46e7606.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_presidential_suite.webp</v>
       </c>
       <c r="B47" t="str">
         <v>src/MockData/room.tsx</v>
       </c>
       <c r="C47">
-        <v>135</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>/africanvillage/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.46e7606.webp</v>
       </c>
       <c r="B48" t="str">
         <v>src/MockData/room.tsx</v>
       </c>
       <c r="C48">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>/entoto/entato1.webp</v>
+        <v>/africanvillage/3.JPG</v>
       </c>
       <c r="B49" t="str">
-        <v>src/MockData/resortsDetails.tsx</v>
+        <v>src/MockData/room.tsx</v>
       </c>
       <c r="C49">
-        <v>16</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>/entoto/entoto.mov</v>
+        <v>/entoto/entato1.webp</v>
       </c>
       <c r="B50" t="str">
         <v>src/MockData/resortsDetails.tsx</v>
       </c>
       <c r="C50">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishAcc.1bbca14.webp</v>
+        <v>/entoto/entoto.mov</v>
       </c>
       <c r="B51" t="str">
         <v>src/MockData/resortsDetails.tsx</v>
       </c>
       <c r="C51">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>/bishoftu/bishoftu.mov</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bishAcc.1bbca14.webp</v>
       </c>
       <c r="B52" t="str">
         <v>src/MockData/resortsDetails.tsx</v>
       </c>
       <c r="C52">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/acc.21e7f6a.webp</v>
+        <v>/bishoftu/bishoftu.mov</v>
       </c>
       <c r="B53" t="str">
         <v>src/MockData/resortsDetails.tsx</v>
       </c>
       <c r="C53">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Accomodation1.c444805.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/acc.21e7f6a.webp</v>
       </c>
       <c r="B54" t="str">
         <v>src/MockData/resortsDetails.tsx</v>
       </c>
       <c r="C54">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>/africanvillage/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Accomodation1.c444805.webp</v>
       </c>
       <c r="B55" t="str">
         <v>src/MockData/resortsDetails.tsx</v>
       </c>
       <c r="C55">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>/africanvillage/africanVillage.MOV</v>
+        <v>/africanvillage/3.JPG</v>
       </c>
       <c r="B56" t="str">
         <v>src/MockData/resortsDetails.tsx</v>
       </c>
       <c r="C56">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-49.jpg</v>
+        <v>/africanvillage/africanVillage.MOV</v>
       </c>
       <c r="B57" t="str">
-        <v>src/MockData/resortsAll.tsx</v>
+        <v>src/MockData/resortsDetails.tsx</v>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-49.jpg</v>
       </c>
       <c r="B58" t="str">
         <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C58">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
       </c>
       <c r="B59" t="str">
         <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C59">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -1056,7 +1056,7 @@
         <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C60">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
@@ -1067,7 +1067,7 @@
         <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C61">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62">
@@ -1078,1294 +1078,1294 @@
         <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C62">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>/africanvillage/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B63" t="str">
-        <v>src/MockData/reservationRooms.tsx</v>
+        <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.46e7606.webp</v>
+        <v>/africanvillage/3.JPG</v>
       </c>
       <c r="B64" t="str">
         <v>src/MockData/reservationRooms.tsx</v>
       </c>
       <c r="C64">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.75aadd4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.46e7606.webp</v>
       </c>
       <c r="B65" t="str">
         <v>src/MockData/reservationRooms.tsx</v>
       </c>
       <c r="C65">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Tana.303f00c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Glamping.75aadd4.webp</v>
       </c>
       <c r="B66" t="str">
         <v>src/MockData/reservationRooms.tsx</v>
       </c>
       <c r="C66">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Adventure.bb2f8d1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Tana.303f00c.webp</v>
       </c>
       <c r="B67" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/reservationRooms.tsx</v>
       </c>
       <c r="C67">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Catering.8818461.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Adventure.bb2f8d1.webp</v>
       </c>
       <c r="B68" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C68">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Adventure.bb2f8d1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Catering.8818461.webp</v>
       </c>
       <c r="B69" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C69">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.e6ec880.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Adventure.bb2f8d1.webp</v>
       </c>
       <c r="B70" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C70">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Kuriftu%20Construction.56c04b5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.e6ec880.webp</v>
       </c>
       <c r="B71" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C71">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Waterpark.0b8de07.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Kuriftu%20Construction.56c04b5.webp</v>
       </c>
       <c r="B72" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C72">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Tana.303f00c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Waterpark.0b8de07.webp</v>
       </c>
       <c r="B73" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C73">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/FeaturedStory.6dcf1a8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Tana.303f00c.webp</v>
       </c>
       <c r="B74" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C74">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>/entoto/entoto.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/FeaturedStory.6dcf1a8.webp</v>
       </c>
       <c r="B75" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C75">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>/bishoftu/bishifto1.webp</v>
+        <v>/entoto/entoto.jpg</v>
       </c>
       <c r="B76" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C76">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>/boston/boston.JPG</v>
+        <v>/bishoftu/bishifto1.webp</v>
       </c>
       <c r="B77" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C77">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>/africanvillage/1.JPG</v>
+        <v>/boston/boston.JPG</v>
       </c>
       <c r="B78" t="str">
         <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C78">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6474ed2.jpg</v>
+        <v>/africanvillage/1.JPG</v>
       </c>
       <c r="B79" t="str">
-        <v>src/MockData/giftVoucher.tsx</v>
+        <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>/entoto/1.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6474ed2.jpg</v>
       </c>
       <c r="B80" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/giftVoucher.tsx</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>/entoto/2.JPG</v>
+        <v>/entoto/1.jpg</v>
       </c>
       <c r="B81" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>/entoto/3.JPG</v>
+        <v>/entoto/2.JPG</v>
       </c>
       <c r="B82" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>/entoto/4.jpg</v>
+        <v>/entoto/3.JPG</v>
       </c>
       <c r="B83" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>/entoto/5.jpg</v>
+        <v>/entoto/4.jpg</v>
       </c>
       <c r="B84" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>/entoto/6.jpg</v>
+        <v>/entoto/5.jpg</v>
       </c>
       <c r="B85" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C85">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>/entoto/7.JPG</v>
+        <v>/entoto/6.jpg</v>
       </c>
       <c r="B86" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C86">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>/entoto/8.JPG</v>
+        <v>/entoto/7.JPG</v>
       </c>
       <c r="B87" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>/entoto/9.jpg</v>
+        <v>/entoto/8.JPG</v>
       </c>
       <c r="B88" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C88">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>/entoto/10.jpg</v>
+        <v>/entoto/9.jpg</v>
       </c>
       <c r="B89" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C89">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>/entoto/11.JPG</v>
+        <v>/entoto/10.jpg</v>
       </c>
       <c r="B90" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C90">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>/entoto/12.JPG</v>
+        <v>/entoto/11.JPG</v>
       </c>
       <c r="B91" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C91">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>/entoto/13.JPG</v>
+        <v>/entoto/12.JPG</v>
       </c>
       <c r="B92" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C92">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>/entoto/14.JPG</v>
+        <v>/entoto/13.JPG</v>
       </c>
       <c r="B93" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C93">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>/entoto/15.JPG</v>
+        <v>/entoto/14.JPG</v>
       </c>
       <c r="B94" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C94">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>/entoto/16.JPG</v>
+        <v>/entoto/15.JPG</v>
       </c>
       <c r="B95" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C95">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>/bishoftu/2.JPG</v>
+        <v>/entoto/16.JPG</v>
       </c>
       <c r="B96" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C96">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>/bishoftu/3.JPG</v>
+        <v>/bishoftu/2.JPG</v>
       </c>
       <c r="B97" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C97">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>/bishoftu/4.JPG</v>
+        <v>/bishoftu/3.JPG</v>
       </c>
       <c r="B98" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C98">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>/bishoftu/5.jpg</v>
+        <v>/bishoftu/4.JPG</v>
       </c>
       <c r="B99" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C99">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>/bishoftu/6.JPG</v>
+        <v>/bishoftu/5.jpg</v>
       </c>
       <c r="B100" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C100">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>/bishoftu/7.JPG</v>
+        <v>/bishoftu/6.JPG</v>
       </c>
       <c r="B101" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C101">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>/bishoftu/8.JPG</v>
+        <v>/bishoftu/7.JPG</v>
       </c>
       <c r="B102" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C102">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>/bishoftu/10.JPG</v>
+        <v>/bishoftu/8.JPG</v>
       </c>
       <c r="B103" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C103">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>/bishoftu/11.JPG</v>
+        <v>/bishoftu/10.JPG</v>
       </c>
       <c r="B104" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C104">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>/bishoftu/12.JPG</v>
+        <v>/bishoftu/11.JPG</v>
       </c>
       <c r="B105" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C105">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>/bishoftu/13.JPG</v>
+        <v>/bishoftu/12.JPG</v>
       </c>
       <c r="B106" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C106">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>/bishoftu/14.JPG</v>
+        <v>/bishoftu/13.JPG</v>
       </c>
       <c r="B107" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C107">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>/bishoftu/15.JPG</v>
+        <v>/bishoftu/14.JPG</v>
       </c>
       <c r="B108" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C108">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
+        <v>/bishoftu/15.JPG</v>
       </c>
       <c r="B109" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C109">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
       </c>
       <c r="B110" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C110">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
       </c>
       <c r="B111" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C111">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching.75afd69.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
       </c>
       <c r="B112" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C112">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching.75afd69.webp</v>
       </c>
       <c r="B113" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C113">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.cba30ab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
       </c>
       <c r="B114" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C114">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.d4feaba.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.cba30ab.webp</v>
       </c>
       <c r="B115" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C115">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.d4feaba.webp</v>
       </c>
       <c r="B116" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C116">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.33fc8c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
       </c>
       <c r="B117" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C117">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/5.9fafbdc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.33fc8c3.webp</v>
       </c>
       <c r="B118" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C118">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun1.6e87593.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/5.9fafbdc.webp</v>
       </c>
       <c r="B119" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C119">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.1b81bb4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun1.6e87593.webp</v>
       </c>
       <c r="B120" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C120">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>/africanvillage/1.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.1b81bb4.webp</v>
       </c>
       <c r="B121" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C121">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>/africanvillage/2.JPG</v>
+        <v>/africanvillage/1.JPG</v>
       </c>
       <c r="B122" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C122">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>/africanvillage/3.JPG</v>
+        <v>/africanvillage/2.JPG</v>
       </c>
       <c r="B123" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C123">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/_DSC5641%20(2)-min.f32edfd.jpg</v>
+        <v>/africanvillage/3.JPG</v>
       </c>
       <c r="B124" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C124">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/waterpark2.7574045.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/_DSC5641%20(2)-min.f32edfd.jpg</v>
       </c>
       <c r="B125" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C125">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/kuriftu%20dec%2022-5391-min%20(1).5f30be4.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/waterpark2.7574045.jpg</v>
       </c>
       <c r="B126" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C126">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/kuriftu%20dec%2022-5422-min%20(1).e20e04c.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/kuriftu%20dec%2022-5391-min%20(1).5f30be4.jpg</v>
       </c>
       <c r="B127" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C127">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide2.ca27dc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/kuriftu%20dec%2022-5422-min%20(1).e20e04c.jpg</v>
       </c>
       <c r="B128" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C128">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.ed0beaf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide2.ca27dc6.webp</v>
       </c>
       <c r="B129" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C129">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/_DSC5820%20(2)-min.c7b8704.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.ed0beaf.webp</v>
       </c>
       <c r="B130" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C130">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TreatByThePorch.df2143d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/_DSC5820%20(2)-min.c7b8704.jpg</v>
       </c>
       <c r="B131" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C131">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide5.e0dfde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TreatByThePorch.df2143d.webp</v>
       </c>
       <c r="B132" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C132">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>/boston/1.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide5.e0dfde1.webp</v>
       </c>
       <c r="B133" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C133">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>/boston/2.JPG</v>
+        <v>/boston/1.JPG</v>
       </c>
       <c r="B134" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C134">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>/boston/3.JPG</v>
+        <v>/boston/2.JPG</v>
       </c>
       <c r="B135" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C135">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>/boston/4.JPG</v>
+        <v>/boston/3.JPG</v>
       </c>
       <c r="B136" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C136">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>/boston/5.JPG</v>
+        <v>/boston/4.JPG</v>
       </c>
       <c r="B137" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C137">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>/boston/6.JPG</v>
+        <v>/boston/5.JPG</v>
       </c>
       <c r="B138" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C138">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>/boston/7.JPG</v>
+        <v>/boston/6.JPG</v>
       </c>
       <c r="B139" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C139">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>/boston/8.JPG</v>
+        <v>/boston/7.JPG</v>
       </c>
       <c r="B140" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C140">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>/boston/9.JPG</v>
+        <v>/boston/8.JPG</v>
       </c>
       <c r="B141" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C141">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/24.9dfafe2.jpg</v>
+        <v>/boston/9.JPG</v>
       </c>
       <c r="B142" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C142">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/25.458bb05.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/24.9dfafe2.jpg</v>
       </c>
       <c r="B143" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C143">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/26.a81e8e3.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/25.458bb05.jpg</v>
       </c>
       <c r="B144" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C144">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/27.cc2beb9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/26.a81e8e3.jpg</v>
       </c>
       <c r="B145" t="str">
         <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C145">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp3.fe1f858.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/27.cc2beb9.jpg</v>
       </c>
       <c r="B146" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C146">
-        <v>10</v>
+        <v>83</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp.0810993.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/exp3.fe1f858.webp</v>
       </c>
       <c r="B147" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C147">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp2.a0ae964.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/exp.0810993.webp</v>
       </c>
       <c r="B148" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C148">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.8b94d4d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/exp2.a0ae964.webp</v>
       </c>
       <c r="B149" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C149">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>/entoto/10.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.8b94d4d.webp</v>
       </c>
       <c r="B150" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C150">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
+        <v>/entoto/10.jpg</v>
       </c>
       <c r="B151" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C151">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fe3.89f2a9f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
       </c>
       <c r="B152" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C152">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>/entoto/bbq.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/fe3.89f2a9f.webp</v>
       </c>
       <c r="B153" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C153">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/feature.7383491.webp</v>
+        <v>/entoto/bbq.jpg</v>
       </c>
       <c r="B154" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C154">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fe2.8b9e86a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/feature.7383491.webp</v>
       </c>
       <c r="B155" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C155">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fe3.89f2a9f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/fe2.8b9e86a.webp</v>
       </c>
       <c r="B156" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C156">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Swimming2.c58b523.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/fe3.89f2a9f.webp</v>
       </c>
       <c r="B157" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C157">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Kayaking.8a09cfa.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Swimming2.c58b523.webp</v>
       </c>
       <c r="B158" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C158">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkF.48a36af.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Kayaking.8a09cfa.webp</v>
       </c>
       <c r="B159" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C159">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Kayaking.8a09cfa.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkF.48a36af.webp</v>
       </c>
       <c r="B160" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C160">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>/bishoftu/8.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Kayaking.8a09cfa.webp</v>
       </c>
       <c r="B161" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C161">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>/bishoftu/3.JPG</v>
+        <v>/bishoftu/8.JPG</v>
       </c>
       <c r="B162" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C162">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Lequanda.ca87f54.webp</v>
+        <v>/bishoftu/3.JPG</v>
       </c>
       <c r="B163" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C163">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching1.9746917.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Lequanda.ca87f54.webp</v>
       </c>
       <c r="B164" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C164">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Hiking.ed4cbf4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching1.9746917.webp</v>
       </c>
       <c r="B165" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C165">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TripToTheFalls.ffa9182.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Hiking.ed4cbf4.webp</v>
       </c>
       <c r="B166" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C166">
-        <v>140</v>
+        <v>126</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TripToTheFalls.ffa9182.webp</v>
       </c>
       <c r="B167" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C167">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CabanaDinig.3d6bf71.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
       </c>
       <c r="B168" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C168">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BoatRide.9d78045.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CabanaDinig.3d6bf71.webp</v>
       </c>
       <c r="B169" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C169">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/BoatRide.9d78045.webp</v>
       </c>
       <c r="B170" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C170">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CabanaDinigLong.f713425.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
       </c>
       <c r="B171" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C171">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SwimmingPoolLong.3075d7d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CabanaDinigLong.f713425.webp</v>
       </c>
       <c r="B172" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C172">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SwimmingPoolLong.3075d7d.webp</v>
       </c>
       <c r="B173" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C173">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching1.15a4456.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
       </c>
       <c r="B174" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C174">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TripToTheFalls.ffa9182.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching1.15a4456.webp</v>
       </c>
       <c r="B175" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C175">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Experience.0da9d1f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TripToTheFalls.ffa9182.webp</v>
       </c>
       <c r="B176" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C176">
-        <v>208</v>
+        <v>194</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre2.7f3adf1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Experience.0da9d1f.webp</v>
       </c>
       <c r="B177" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C177">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/awash-cover.8aba739.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre2.7f3adf1.webp</v>
       </c>
       <c r="B178" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C178">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CamelRide.3ed74a1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/awash-cover.8aba739.webp</v>
       </c>
       <c r="B179" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C179">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="180">
@@ -2376,3175 +2376,3175 @@
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C180">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fe3.89f2a9f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CamelRide.3ed74a1.webp</v>
       </c>
       <c r="B181" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C181">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Yoga.3b1b821.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/fe3.89f2a9f.webp</v>
       </c>
       <c r="B182" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C182">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long3.cd91821.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Yoga.3b1b821.webp</v>
       </c>
       <c r="B183" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C183">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>/spa/spa3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long3.cd91821.webp</v>
       </c>
       <c r="B184" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C184">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/PrivateEvent.6edee64.webp</v>
+        <v>/spa/spa3.JPG</v>
       </c>
       <c r="B185" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C185">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BreakfastInTheDesert.bcdd2cd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/PrivateEvent.6edee64.webp</v>
       </c>
       <c r="B186" t="str">
         <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C186">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/BreakfastInTheDesert.bcdd2cd.webp</v>
       </c>
       <c r="B187" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C187">
-        <v>10</v>
+        <v>264</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
       </c>
       <c r="B188" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C188">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s3.38a710c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
       </c>
       <c r="B189" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C189">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s3.38a710c.webp</v>
       </c>
       <c r="B190" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C190">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>/entoto/8.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
       </c>
       <c r="B191" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C191">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Birthday.3362d09.webp</v>
+        <v>/entoto/8.JPG</v>
       </c>
       <c r="B192" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C192">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SocialEvent.f486a56.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Birthday.3362d09.webp</v>
       </c>
       <c r="B193" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C193">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingVenue.4c9426b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SocialEvent.f486a56.webp</v>
       </c>
       <c r="B194" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C194">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Open%20Air.4abd236.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingVenue.4c9426b.webp</v>
       </c>
       <c r="B195" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C195">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/InDoor.4253f5a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Open%20Air.4abd236.webp</v>
       </c>
       <c r="B196" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C196">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/InDoor.4253f5a.webp</v>
       </c>
       <c r="B197" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C197">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.9e5c587.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
       </c>
       <c r="B198" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C198">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.30afcb1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.9e5c587.webp</v>
       </c>
       <c r="B199" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C199">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.a740033.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.30afcb1.webp</v>
       </c>
       <c r="B200" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C200">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.a740033.webp</v>
       </c>
       <c r="B201" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C201">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/waterpark.9066e15.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
       </c>
       <c r="B202" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C202">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/waterpark.9066e15.webp</v>
       </c>
       <c r="B203" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C203">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
       </c>
       <c r="B204" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C204">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.0cf4a1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
       </c>
       <c r="B205" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C205">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.0cf4a1d.webp</v>
       </c>
       <c r="B206" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C206">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
       </c>
       <c r="B207" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C207">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/concert.e1cdbcd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
       </c>
       <c r="B208" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C208">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/social.c5ddebd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/concert.e1cdbcd.webp</v>
       </c>
       <c r="B209" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C209">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/social.c5ddebd.webp</v>
       </c>
       <c r="B210" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C210">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.a740033.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
       </c>
       <c r="B211" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C211">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Cabbana.911be42.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.a740033.webp</v>
       </c>
       <c r="B212" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C212">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/waterpark.9066e15.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Cabbana.911be42.webp</v>
       </c>
       <c r="B213" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C213">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/waterpark.9066e15.webp</v>
       </c>
       <c r="B214" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C214">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.9e5c587.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
       </c>
       <c r="B215" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C215">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.30afcb1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.9e5c587.webp</v>
       </c>
       <c r="B216" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C216">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.30afcb1.webp</v>
       </c>
       <c r="B217" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C217">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
       </c>
       <c r="B218" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C218">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Cabana.2f03513.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
       </c>
       <c r="B219" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C219">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Cabana.2f03513.webp</v>
       </c>
       <c r="B220" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C220">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
       </c>
       <c r="B221" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C221">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
       </c>
       <c r="B222" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C222">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
       </c>
       <c r="B223" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C223">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
       </c>
       <c r="B224" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C224">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Cabana.2f03513.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
       </c>
       <c r="B225" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C225">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.0111b85.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Cabana.2f03513.webp</v>
       </c>
       <c r="B226" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C226">
-        <v>272</v>
+        <v>263</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.f4ccdbc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.0111b85.webp</v>
       </c>
       <c r="B227" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C227">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.19a424e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.f4ccdbc.webp</v>
       </c>
       <c r="B228" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C228">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.19a424e.webp</v>
       </c>
       <c r="B229" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C229">
-        <v>299</v>
+        <v>288</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wedding.b762def.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
       </c>
       <c r="B230" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C230">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Birthdays.cd4c5d2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wedding.b762def.webp</v>
       </c>
       <c r="B231" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C231">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SocialEvents.8fadfab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Birthdays.cd4c5d2.webp</v>
       </c>
       <c r="B232" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C232">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SocialEvents.8fadfab.webp</v>
       </c>
       <c r="B233" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C233">
-        <v>344</v>
+        <v>325</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
       </c>
       <c r="B234" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C234">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s3.38a710c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
       </c>
       <c r="B235" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C235">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.628f404.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s3.38a710c.webp</v>
       </c>
       <c r="B236" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C236">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.628f404.webp</v>
       </c>
       <c r="B237" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C237">
-        <v>362</v>
+        <v>354</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
       </c>
       <c r="B238" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C238">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/we.c516b54.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
       </c>
       <c r="B239" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C239">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/we.c516b54.webp</v>
       </c>
       <c r="B240" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C240">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
       </c>
       <c r="B241" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C241">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.628f404.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
       </c>
       <c r="B242" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C242">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.628f404.webp</v>
       </c>
       <c r="B243" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C243">
-        <v>389</v>
+        <v>377</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
       </c>
       <c r="B244" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C244">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
       </c>
       <c r="B245" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C245">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e579177.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
       </c>
       <c r="B246" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C246">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e579177.webp</v>
       </c>
       <c r="B247" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C247">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
       </c>
       <c r="B248" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C248">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingLong.07f0acc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
       </c>
       <c r="B249" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C249">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingLong.07f0acc.webp</v>
       </c>
       <c r="B250" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C250">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
       </c>
       <c r="B251" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C251">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.b4fafda.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
       </c>
       <c r="B252" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C252">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.b4fafda.webp</v>
       </c>
       <c r="B253" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C253">
-        <v>434</v>
+        <v>422</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
       </c>
       <c r="B254" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C254">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e579177.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
       </c>
       <c r="B255" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C255">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e579177.webp</v>
       </c>
       <c r="B256" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C256">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
       </c>
       <c r="B257" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C257">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.b4fafda.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
       </c>
       <c r="B258" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C258">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingLong.07f0acc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.b4fafda.webp</v>
       </c>
       <c r="B259" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C259">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingLong.07f0acc.webp</v>
       </c>
       <c r="B260" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C260">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
       </c>
       <c r="B261" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C261">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
       </c>
       <c r="B262" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C262">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e3ecdac.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
       </c>
       <c r="B263" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C263">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e3ecdac.webp</v>
       </c>
       <c r="B264" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C264">
-        <v>491</v>
+        <v>483</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
       </c>
       <c r="B265" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C265">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Mels.d221dee.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
       </c>
       <c r="B266" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C266">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wedding1.4c034c6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Mels.d221dee.webp</v>
       </c>
       <c r="B267" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C267">
-        <v>512</v>
+        <v>505</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Honeymoon.c509471.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wedding1.4c034c6.webp</v>
       </c>
       <c r="B268" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C268">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/7.2dae83c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Honeymoon.c509471.webp</v>
       </c>
       <c r="B269" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C269">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/10.60d29d1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/7.2dae83c.webp</v>
       </c>
       <c r="B270" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C270">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.726df95.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/10.60d29d1.webp</v>
       </c>
       <c r="B271" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C271">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.cba30ab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.726df95.webp</v>
       </c>
       <c r="B272" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C272">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.b337c8c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.cba30ab.webp</v>
       </c>
       <c r="B273" t="str">
         <v>src/MockData/events.tsx</v>
       </c>
       <c r="C273">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.b337c8c.webp</v>
       </c>
       <c r="B274" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C274">
-        <v>5</v>
+        <v>527</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
       </c>
       <c r="B275" t="str">
         <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C275">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
       </c>
       <c r="B276" t="str">
         <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C276">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
       </c>
       <c r="B277" t="str">
         <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C277">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>/images/event.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
       </c>
       <c r="B278" t="str">
         <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C278">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>/spa/spa1.JPG</v>
+        <v>/images/event.jpg</v>
       </c>
       <c r="B279" t="str">
         <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C279">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>/spa/spa2.JPG</v>
+        <v>/spa/spa1.JPG</v>
       </c>
       <c r="B280" t="str">
         <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C280">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>/spa/spa3.JPG</v>
+        <v>/spa/spa2.JPG</v>
       </c>
       <c r="B281" t="str">
         <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C281">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>/spa/spa4.JPG</v>
+        <v>/spa/spa3.JPG</v>
       </c>
       <c r="B282" t="str">
         <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C282">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
+        <v>/spa/spa4.JPG</v>
       </c>
       <c r="B283" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C283">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
       </c>
       <c r="B284" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C284">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
       </c>
       <c r="B285" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C285">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
       </c>
       <c r="B286" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C286">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheRidersRanch.2035096.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
       </c>
       <c r="B287" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C287">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CastelBar&amp;Grill.1f72ad2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheRidersRanch.2035096.webp</v>
       </c>
       <c r="B288" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C288">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheMarksmanBar&amp;Grill.0af1692.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CastelBar&amp;Grill.1f72ad2.webp</v>
       </c>
       <c r="B289" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C289">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/PitStopBar&amp;Grill.d7a6bea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheMarksmanBar&amp;Grill.0af1692.webp</v>
       </c>
       <c r="B290" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C290">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/FamilyDining.7a275ef.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/PitStopBar&amp;Grill.d7a6bea.webp</v>
       </c>
       <c r="B291" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C291">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ArcheryCallenge.4956286.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/FamilyDining.7a275ef.webp</v>
       </c>
       <c r="B292" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C292">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.82d1f76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ArcheryCallenge.4956286.webp</v>
       </c>
       <c r="B293" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C293">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeFront.55a2ad2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.82d1f76.webp</v>
       </c>
       <c r="B294" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C294">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Lequanda.9dcb7ac.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeFront.55a2ad2.webp</v>
       </c>
       <c r="B295" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C295">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkCabanas.00f0dde.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Lequanda.9dcb7ac.webp</v>
       </c>
       <c r="B296" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C296">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkDiner.e837424.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkCabanas.00f0dde.webp</v>
       </c>
       <c r="B297" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C297">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Cabbana.911be42.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkDiner.e837424.webp</v>
       </c>
       <c r="B298" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C298">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeFrontF.37dd2a9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Cabbana.911be42.webp</v>
       </c>
       <c r="B299" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C299">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CabbanaF.295b550.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeFrontF.37dd2a9.webp</v>
       </c>
       <c r="B300" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C300">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LequandaF.73439a0.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CabbanaF.295b550.webp</v>
       </c>
       <c r="B301" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C301">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkDinerF.f8a74fa.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LequandaF.73439a0.webp</v>
       </c>
       <c r="B302" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C302">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkCabanasO.a6a031a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkDinerF.f8a74fa.webp</v>
       </c>
       <c r="B303" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C303">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffetO.ea5b225.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkCabanasO.a6a031a.webp</v>
       </c>
       <c r="B304" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C304">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.89ba262.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffetO.ea5b225.webp</v>
       </c>
       <c r="B305" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C305">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.89ba262.webp</v>
       </c>
       <c r="B306" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C306">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.7c07513.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
       </c>
       <c r="B307" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C307">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.a30d654.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.7c07513.webp</v>
       </c>
       <c r="B308" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C308">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.7c07513.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.a30d654.webp</v>
       </c>
       <c r="B309" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C309">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.7c07513.webp</v>
       </c>
       <c r="B310" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C310">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.89ba262.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
       </c>
       <c r="B311" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C311">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.a30d654.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.89ba262.webp</v>
       </c>
       <c r="B312" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C312">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.a30d654.webp</v>
       </c>
       <c r="B313" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C313">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ThePoolBar&amp;Grill.33fc8c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
       </c>
       <c r="B314" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C314">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/din1.79ddaae.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ThePoolBar&amp;Grill.33fc8c3.webp</v>
       </c>
       <c r="B315" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C315">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/din2.2a7cebb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/din1.79ddaae.webp</v>
       </c>
       <c r="B316" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C316">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/din3.10849d7.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/din2.2a7cebb.webp</v>
       </c>
       <c r="B317" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C317">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/din3.10849d7.webp</v>
       </c>
       <c r="B318" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C318">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ThePoolBar&amp;Grill.33fc8c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
       </c>
       <c r="B319" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C319">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide.d5ccc8b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ThePoolBar&amp;Grill.33fc8c3.webp</v>
       </c>
       <c r="B320" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C320">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide2.ca27dc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide.d5ccc8b.webp</v>
       </c>
       <c r="B321" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C321">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide3.7e0fcf3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide2.ca27dc6.webp</v>
       </c>
       <c r="B322" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C322">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide4.8b1e6bb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide3.7e0fcf3.webp</v>
       </c>
       <c r="B323" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C323">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide5.e0dfde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide4.8b1e6bb.webp</v>
       </c>
       <c r="B324" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C324">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide6.d93b9ac.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide5.e0dfde1.webp</v>
       </c>
       <c r="B325" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C325">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Plaza.a45b650.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide6.d93b9ac.webp</v>
       </c>
       <c r="B326" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C326">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.ed0beaf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Plaza.a45b650.webp</v>
       </c>
       <c r="B327" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C327">
-        <v>237</v>
+        <v>228</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TreatByThePorch.df2143d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.ed0beaf.webp</v>
       </c>
       <c r="B328" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C328">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ReserveATable.b368639.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TreatByThePorch.df2143d.webp</v>
       </c>
       <c r="B329" t="str">
         <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C329">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/contact.2e8edc6.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ReserveATable.b368639.webp</v>
       </c>
       <c r="B330" t="str">
-        <v>src/MockData/contactUsData.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C330">
-        <v>2</v>
+        <v>249</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>/images/contact.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/contact.2e8edc6.jpg</v>
       </c>
       <c r="B331" t="str">
         <v>src/MockData/contactUsData.tsx</v>
       </c>
       <c r="C331">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s5.52f7de0.webp</v>
+        <v>/images/contact.jpg</v>
       </c>
       <c r="B332" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/contactUsData.tsx</v>
       </c>
       <c r="C332">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s5.52f7de0.webp</v>
       </c>
       <c r="B333" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C333">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
       </c>
       <c r="B334" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C334">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
       </c>
       <c r="B335" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C335">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>/entoto/5.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
       </c>
       <c r="B336" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C336">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/re.0af1692.webp</v>
+        <v>/entoto/5.jpg</v>
       </c>
       <c r="B337" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C337">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/conf.5532829.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/re.0af1692.webp</v>
       </c>
       <c r="B338" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C338">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/MultiPurposeCabin.8dde207.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/conf.5532829.webp</v>
       </c>
       <c r="B339" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C339">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/MultiPurposeCabin.8dde207.webp</v>
       </c>
       <c r="B340" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C340">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheRidersRanch.2035096.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
       </c>
       <c r="B341" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C341">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CastelBar&amp;Grill.1f72ad2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheRidersRanch.2035096.webp</v>
       </c>
       <c r="B342" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C342">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CastelBar&amp;Grill.1f72ad2.webp</v>
       </c>
       <c r="B343" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C343">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SpaceOrganization.d5320f2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
       </c>
       <c r="B344" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C344">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ClosingEvent.dee1570.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SpaceOrganization.d5320f2.webp</v>
       </c>
       <c r="B345" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C345">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ClosingEvent.dee1570.webp</v>
       </c>
       <c r="B346" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C346">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
       </c>
       <c r="B347" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C347">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.0cf4a1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
       </c>
       <c r="B348" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C348">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.a740033.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.0cf4a1d.webp</v>
       </c>
       <c r="B349" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C349">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.a740033.webp</v>
       </c>
       <c r="B350" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C350">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/waterpark.9066e15.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
       </c>
       <c r="B351" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C351">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1F.2b483af.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/waterpark.9066e15.webp</v>
       </c>
       <c r="B352" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C352">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2F.571751b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1F.2b483af.webp</v>
       </c>
       <c r="B353" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C353">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3F.c2b11a7.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2F.571751b.webp</v>
       </c>
       <c r="B354" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C354">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3F.c2b11a7.webp</v>
       </c>
       <c r="B355" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C355">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
       </c>
       <c r="B356" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C356">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.0cf4a1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
       </c>
       <c r="B357" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C357">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.a54c78e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.0cf4a1d.webp</v>
       </c>
       <c r="B358" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C358">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/catering.9294532.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.a54c78e.webp</v>
       </c>
       <c r="B359" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C359">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1O.5433205.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/catering.9294532.webp</v>
       </c>
       <c r="B360" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C360">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2O.754ae7c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1O.5433205.webp</v>
       </c>
       <c r="B361" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C361">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2O.754ae7c.webp</v>
       </c>
       <c r="B362" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C362">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
       </c>
       <c r="B363" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C363">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateRetreat.3b7233d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
       </c>
       <c r="B364" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C364">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateRetreat.3b7233d.webp</v>
       </c>
       <c r="B365" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C365">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
       </c>
       <c r="B366" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C366">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateRetreat.3b7233d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
       </c>
       <c r="B367" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C367">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateRetreat.3b7233d.webp</v>
       </c>
       <c r="B368" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C368">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
       </c>
       <c r="B369" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C369">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
       </c>
       <c r="B370" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C370">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
       </c>
       <c r="B371" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C371">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/co.e67c272.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
       </c>
       <c r="B372" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C372">
-        <v>291</v>
+        <v>278</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/co2.c47cb91.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/co.e67c272.webp</v>
       </c>
       <c r="B373" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C373">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Co3.931a172.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/co2.c47cb91.webp</v>
       </c>
       <c r="B374" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C374">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/co2.c47cb91.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Co3.931a172.webp</v>
       </c>
       <c r="B375" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C375">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/co.e67c272.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/co2.c47cb91.webp</v>
       </c>
       <c r="B376" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C376">
-        <v>319</v>
+        <v>309</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.1e370ba.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/co.e67c272.webp</v>
       </c>
       <c r="B377" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C377">
-        <v>330</v>
+        <v>319</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SpaceOrganization.4284dbb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.1e370ba.webp</v>
       </c>
       <c r="B378" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C378">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ClosingEvent.1e10bb5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SpaceOrganization.4284dbb.webp</v>
       </c>
       <c r="B379" t="str">
         <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C379">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ArtGallery.cb59c6c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ClosingEvent.1e10bb5.webp</v>
       </c>
       <c r="B380" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C380">
-        <v>13</v>
+        <v>345</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>/spa/spa2.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ArtGallery.cb59c6c.webp</v>
       </c>
       <c r="B381" t="str">
         <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C381">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SteamSaunaJaccuzi.644ea57.webp</v>
+        <v>/spa/spa2.JPG</v>
       </c>
       <c r="B382" t="str">
         <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C382">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Massage.ce5f64d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SteamSaunaJaccuzi.644ea57.webp</v>
       </c>
       <c r="B383" t="str">
         <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C383">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Massage.ce5f64d.webp</v>
       </c>
       <c r="B384" t="str">
         <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C384">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaxLong.cb4bf93.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B385" t="str">
         <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C385">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ManiPediLong.e819bca.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaxLong.cb4bf93.webp</v>
       </c>
       <c r="B386" t="str">
         <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C386">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Massage.ce5f64d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ManiPediLong.e819bca.webp</v>
       </c>
       <c r="B387" t="str">
         <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C387">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/hair.96d890e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Massage.ce5f64d.webp</v>
       </c>
       <c r="B388" t="str">
         <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C388">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Barber.4bc1f30.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/hair.96d890e.webp</v>
       </c>
       <c r="B389" t="str">
         <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C389">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/AfricaRoomBed.28e54c2.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Barber.4bc1f30.webp</v>
       </c>
       <c r="B390" t="str">
-        <v>src/MockData/africanVillageAccomodation.tsx</v>
+        <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C390">
-        <v>30</v>
+        <v>92</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/AfricaRestaurant.36863f2.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/AfricaRoomBed.28e54c2.jpg</v>
       </c>
       <c r="B391" t="str">
         <v>src/MockData/africanVillageAccomodation.tsx</v>
       </c>
       <c r="C391">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/AfricaMassage.ff8ac7b.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/AfricaRestaurant.36863f2.jpg</v>
       </c>
       <c r="B392" t="str">
         <v>src/MockData/africanVillageAccomodation.tsx</v>
       </c>
       <c r="C392">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2bb9fd7.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/AfricaMassage.ff8ac7b.jpg</v>
       </c>
       <c r="B393" t="str">
-        <v>src/MockData/adventure.tsx</v>
+        <v>src/MockData/africanVillageAccomodation.tsx</v>
       </c>
       <c r="C393">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.609dbb9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2bb9fd7.webp</v>
       </c>
       <c r="B394" t="str">
         <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C394">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.89f1f99.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.609dbb9.webp</v>
       </c>
       <c r="B395" t="str">
         <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C395">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/hors.1e1048c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.89f1f99.webp</v>
       </c>
       <c r="B396" t="str">
         <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C396">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/zip.c6c6a45.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/hors.1e1048c.webp</v>
       </c>
       <c r="B397" t="str">
         <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C397">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/play.54f31e5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/zip.c6c6a45.webp</v>
       </c>
       <c r="B398" t="str">
         <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C398">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/play.54f31e5.webp</v>
       </c>
       <c r="B399" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C399">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
       </c>
       <c r="B400" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C400">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
       </c>
       <c r="B401" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C401">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B402" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C402">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.1424c84.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
       </c>
       <c r="B403" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C403">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.5c6074e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.1424c84.webp</v>
       </c>
       <c r="B404" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C404">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.5c6074e.webp</v>
       </c>
       <c r="B405" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C405">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B406" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C406">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
       </c>
       <c r="B407" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C407">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Premium.eb88e0f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
       </c>
       <c r="B408" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C408">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Junior.d5ce7f3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Premium.eb88e0f.webp</v>
       </c>
       <c r="B409" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C409">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Experience.56a6110.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Junior.d5ce7f3.webp</v>
       </c>
       <c r="B410" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C410">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.7f3adf1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Experience.56a6110.webp</v>
       </c>
       <c r="B411" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C411">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.7f3adf1.webp</v>
       </c>
       <c r="B412" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C412">
-        <v>160</v>
+        <v>143</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/5.1d56014.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
       </c>
       <c r="B413" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C413">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/5.1d56014.webp</v>
       </c>
       <c r="B414" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C414">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
       </c>
       <c r="B415" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C415">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/slide2.2.33da435.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
       </c>
       <c r="B416" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C416">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/slide2.2.33da435.webp</v>
       </c>
       <c r="B417" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C417">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.64d69d1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
       </c>
       <c r="B418" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C418">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.1ea7836.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.64d69d1.webp</v>
       </c>
       <c r="B419" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C419">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.59933f3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.1ea7836.webp</v>
       </c>
       <c r="B420" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C420">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.9e6f0ca.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.59933f3.webp</v>
       </c>
       <c r="B421" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C421">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0cc943d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.9e6f0ca.webp</v>
       </c>
       <c r="B422" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C422">
-        <v>240</v>
+        <v>227</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.b0c6e49.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0cc943d.webp</v>
       </c>
       <c r="B423" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C423">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.12d11d4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.b0c6e49.webp</v>
       </c>
       <c r="B424" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C424">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.d471ca4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.12d11d4.webp</v>
       </c>
       <c r="B425" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C425">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.d471ca4.webp</v>
       </c>
       <c r="B426" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C426">
-        <v>263</v>
+        <v>243</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
       </c>
       <c r="B427" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C427">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
       </c>
       <c r="B428" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C428">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.eb2af55.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
       </c>
       <c r="B429" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C429">
-        <v>291</v>
+        <v>281</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.fcb2c4b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.eb2af55.webp</v>
       </c>
       <c r="B430" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C430">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.95ea902.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.fcb2c4b.webp</v>
       </c>
       <c r="B431" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C431">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.12d11d4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.95ea902.webp</v>
       </c>
       <c r="B432" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C432">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/gardenLong.f325f95.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.12d11d4.webp</v>
       </c>
       <c r="B433" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C433">
-        <v>313</v>
+        <v>294</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/gardenLong2.a5ba8bc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/gardenLong.f325f95.webp</v>
       </c>
       <c r="B434" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C434">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/gardenLong2.a5ba8bc.webp</v>
       </c>
       <c r="B435" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C435">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B436" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C436">
-        <v>332</v>
+        <v>322</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
       </c>
       <c r="B437" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C437">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0052dfd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
       </c>
       <c r="B438" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C438">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.2faa8da.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0052dfd.webp</v>
       </c>
       <c r="B439" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C439">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.8096683.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.2faa8da.webp</v>
       </c>
       <c r="B440" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C440">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.0a26366.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.8096683.webp</v>
       </c>
       <c r="B441" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C441">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long1.f233b2e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.0a26366.webp</v>
       </c>
       <c r="B442" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C442">
-        <v>374</v>
+        <v>353</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.d8e3c85.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long1.f233b2e.webp</v>
       </c>
       <c r="B443" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C443">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.d8e3c85.webp</v>
       </c>
       <c r="B444" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C444">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B445" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C445">
-        <v>390</v>
+        <v>381</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
       </c>
       <c r="B446" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C446">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.020c051.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
       </c>
       <c r="B447" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C447">
-        <v>409</v>
+        <v>399</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.5c6074e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.020c051.webp</v>
       </c>
       <c r="B448" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C448">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.65258bc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.5c6074e.webp</v>
       </c>
       <c r="B449" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C449">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.6510504.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.65258bc.webp</v>
       </c>
       <c r="B450" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C450">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.6510504.webp</v>
       </c>
       <c r="B451" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C451">
-        <v>433</v>
+        <v>412</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
       </c>
       <c r="B452" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C452">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
       </c>
       <c r="B453" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C453">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B454" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C454">
-        <v>447</v>
+        <v>440</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
       </c>
       <c r="B455" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C455">
-        <v>456</v>
+        <v>447</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
       </c>
       <c r="B456" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C456">
-        <v>469</v>
+        <v>456</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/acc.21e7f6a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B457" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C457">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Lake%20View.8450a33.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/acc.21e7f6a.webp</v>
       </c>
       <c r="B458" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C458">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Lake%20View.8450a33.jpg</v>
       </c>
       <c r="B459" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C459">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
       </c>
       <c r="B460" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C460">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
       </c>
       <c r="B461" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C461">
-        <v>496</v>
+        <v>476</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
       </c>
       <c r="B462" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C462">
-        <v>503</v>
+        <v>496</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.f4dec86.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B463" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C463">
-        <v>513</v>
+        <v>503</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.f4dec86.webp</v>
       </c>
       <c r="B464" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C464">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2Long.e5c90e2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
       </c>
       <c r="B465" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C465">
-        <v>532</v>
+        <v>514</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1Long.0f24bb8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2Long.e5c90e2.webp</v>
       </c>
       <c r="B466" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C466">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1Long.0f24bb8.webp</v>
       </c>
       <c r="B467" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C467">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B468" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C468">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="469">
@@ -5555,513 +5555,513 @@
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C469">
-        <v>557</v>
+        <v>548</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
       </c>
       <c r="B470" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C470">
-        <v>574</v>
+        <v>557</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
       </c>
       <c r="B471" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C471">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
       </c>
       <c r="B472" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C472">
-        <v>581</v>
+        <v>575</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
       </c>
       <c r="B473" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C473">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/prem1.ac33bc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B474" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C474">
-        <v>602</v>
+        <v>590</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/prem3.9946e8a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/prem1.ac33bc2.webp</v>
       </c>
       <c r="B475" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C475">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/prem2.37ca344.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/prem3.9946e8a.webp</v>
       </c>
       <c r="B476" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C476">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long1.d4959d9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/prem2.37ca344.webp</v>
       </c>
       <c r="B477" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C477">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.2c20677.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long1.d4959d9.webp</v>
       </c>
       <c r="B478" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C478">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.2c20677.webp</v>
       </c>
       <c r="B479" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C479">
-        <v>632</v>
+        <v>612</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
       </c>
       <c r="B480" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C480">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
       </c>
       <c r="B481" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C481">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun2.c4d959a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
       </c>
       <c r="B482" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C482">
-        <v>658</v>
+        <v>648</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun4.d5ce7f3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun2.c4d959a.webp</v>
       </c>
       <c r="B483" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C483">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun3.ac33bc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun4.d5ce7f3.webp</v>
       </c>
       <c r="B484" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C484">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun1.6e87593.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun3.ac33bc2.webp</v>
       </c>
       <c r="B485" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C485">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.939d932.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun1.6e87593.webp</v>
       </c>
       <c r="B486" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C486">
-        <v>681</v>
+        <v>661</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.362c90f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.939d932.webp</v>
       </c>
       <c r="B487" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C487">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.362c90f.webp</v>
       </c>
       <c r="B488" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C488">
-        <v>688</v>
+        <v>682</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
       </c>
       <c r="B489" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C489">
-        <v>695</v>
+        <v>688</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
       </c>
       <c r="B490" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C490">
-        <v>702</v>
+        <v>695</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Executive.56a6110.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
       </c>
       <c r="B491" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C491">
-        <v>712</v>
+        <v>702</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/RIH03650.7e26c7e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Executive.56a6110.webp</v>
       </c>
       <c r="B492" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C492">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.056bfc0.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/RIH03650.7e26c7e.webp</v>
       </c>
       <c r="B493" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C493">
-        <v>733</v>
+        <v>713</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.a79d619.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.056bfc0.webp</v>
       </c>
       <c r="B494" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C494">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.a79d619.webp</v>
       </c>
       <c r="B495" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C495">
-        <v>740</v>
+        <v>734</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
       </c>
       <c r="B496" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C496">
-        <v>747</v>
+        <v>740</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
       </c>
       <c r="B497" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C497">
-        <v>754</v>
+        <v>747</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre2.7f3adf1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
       </c>
       <c r="B498" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C498">
-        <v>764</v>
+        <v>754</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre1.43b4f0d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre2.7f3adf1.webp</v>
       </c>
       <c r="B499" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C499">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre5.c47cb91.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre1.43b4f0d.webp</v>
       </c>
       <c r="B500" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C500">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre3.e77e1ff.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre5.c47cb91.webp</v>
       </c>
       <c r="B501" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C501">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.f2c0a75.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre3.e77e1ff.webp</v>
       </c>
       <c r="B502" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C502">
-        <v>787</v>
+        <v>767</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.47e592b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.f2c0a75.webp</v>
       </c>
       <c r="B503" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C503">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.47e592b.webp</v>
       </c>
       <c r="B504" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C504">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
       </c>
       <c r="B505" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C505">
-        <v>801</v>
+        <v>794</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
       </c>
       <c r="B506" t="str">
         <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C506">
-        <v>808</v>
+        <v>801</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/IMG-20210910-WA0004.5ca1b87.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
       </c>
       <c r="B507" t="str">
-        <v>src/MockData/aboutUsPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C507">
-        <v>5</v>
+        <v>808</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/aboutusafrica.c7a6efc.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/IMG-20210910-WA0004.5ca1b87.jpg</v>
       </c>
       <c r="B508" t="str">
         <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C508">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pic2.16ba64d.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/aboutusafrica.c7a6efc.jpg</v>
       </c>
       <c r="B509" t="str">
         <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C509">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/p2.8eb6b5f.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pic2.16ba64d.jpg</v>
       </c>
       <c r="B510" t="str">
         <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C510">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/p2.8eb6b5f.jpg</v>
       </c>
       <c r="B511" t="str">
         <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C511">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>/images/landing/apeal.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
       </c>
       <c r="B512" t="str">
-        <v>src/Data/static_text.tsx</v>
+        <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C512">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-49.jpg</v>
+        <v>/images/landing/apeal.JPG</v>
       </c>
       <c r="B513" t="str">
-        <v>src/Data/resort.tsx</v>
+        <v>src/Data/static_text.tsx</v>
       </c>
       <c r="C513">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-49.jpg</v>
       </c>
       <c r="B514" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C514">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
       </c>
       <c r="B515" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C515">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="516">
@@ -6072,7 +6072,7 @@
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C516">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="517">
@@ -6083,7 +6083,7 @@
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C517">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="518">
@@ -6094,23 +6094,23 @@
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C518">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B519" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C519">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B520" t="str">
         <v>src/Data/resort.tsx</v>
@@ -6121,227 +6121,227 @@
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-6.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B521" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C521">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-35.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-6.jpg</v>
       </c>
       <c r="B522" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C522">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-28.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-35.jpg</v>
       </c>
       <c r="B523" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C523">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-40.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-28.jpg</v>
       </c>
       <c r="B524" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C524">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-79.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-40.jpg</v>
       </c>
       <c r="B525" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C525">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-76.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-79.jpg</v>
       </c>
       <c r="B526" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C526">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-26.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-76.jpg</v>
       </c>
       <c r="B527" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C527">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-26.jpg</v>
       </c>
       <c r="B528" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C528">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B529" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C529">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B530" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C530">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B531" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C531">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B532" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C532">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B533" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C533">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-20.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B534" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C534">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-20.jpg</v>
       </c>
       <c r="B535" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C535">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-51.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B536" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C536">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-49.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-51.jpg</v>
       </c>
       <c r="B537" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C537">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>https://example.com/images/boston-day-spa-1.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-49.jpg</v>
       </c>
       <c r="B538" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C538">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-24.jpg</v>
+        <v>https://example.com/images/boston-day-spa-1.jpg</v>
       </c>
       <c r="B539" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C539">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-24.jpg</v>
       </c>
       <c r="B540" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C540">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B541" t="str">
         <v>src/Data/resort.tsx</v>
@@ -6352,117 +6352,117 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7930.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B542" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C542">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8509.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7930.jpg</v>
       </c>
       <c r="B543" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C543">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC9136.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8509.jpg</v>
       </c>
       <c r="B544" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C544">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7935.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC9136.jpg</v>
       </c>
       <c r="B545" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C545">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8814.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7935.jpg</v>
       </c>
       <c r="B546" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C546">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/go.8dde4b1.webp</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8814.jpg</v>
       </c>
       <c r="B547" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C547">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8532.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/go.8dde4b1.webp</v>
       </c>
       <c r="B548" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C548">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8532.jpg</v>
       </c>
       <c r="B549" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C549">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/Entoto+Final+.mov</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
       </c>
       <c r="B550" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C550">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/Entoto+Final+.mov</v>
       </c>
       <c r="B551" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C551">
-        <v>148</v>
+        <v>132</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B552" t="str">
         <v>src/Data/resort.tsx</v>
@@ -6473,227 +6473,227 @@
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B553" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C553">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B554" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C554">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B555" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C555">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B556" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C556">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B557" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C557">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B558" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C558">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B559" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C559">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B560" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C560">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B561" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C561">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B562" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C562">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B563" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C563">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B564" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C564">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B565" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C565">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B566" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C566">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B567" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C567">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B568" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C568">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/gallery2.e8d5a67.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B569" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C569">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>https://example.com/images/kuriftu-awash-1.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/gallery2.e8d5a67.webp</v>
       </c>
       <c r="B570" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C570">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>https://example.com/images/kuriftu-awash-2.jpg</v>
+        <v>https://example.com/images/kuriftu-awash-1.jpg</v>
       </c>
       <c r="B571" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C571">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
+        <v>https://example.com/images/kuriftu-awash-2.jpg</v>
       </c>
       <c r="B572" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C572">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B573" t="str">
         <v>src/Data/resort.tsx</v>
@@ -6704,227 +6704,227 @@
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B574" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C574">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B575" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C575">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B576" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C576">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B577" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C577">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B578" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C578">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B579" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C579">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B580" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C580">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B581" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C581">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B582" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C582">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B583" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C583">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B584" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C584">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B585" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C585">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B586" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C586">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B587" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C587">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B588" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C588">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B589" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C589">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B590" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C590">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu-1.jpg</v>
+        <v>https://example.com/images/kuriftu-bishoftu.jpg</v>
       </c>
       <c r="B591" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C591">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu-2.jpg</v>
+        <v>https://example.com/images/kuriftu-bishoftu-1.jpg</v>
       </c>
       <c r="B592" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C592">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
+        <v>https://example.com/images/kuriftu-bishoftu-2.jpg</v>
       </c>
       <c r="B593" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C593">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B594" t="str">
         <v>src/Data/resort.tsx</v>
@@ -6935,227 +6935,227 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B595" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C595">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B596" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C596">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B597" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C597">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B598" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C598">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B599" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C599">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B600" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C600">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B601" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C601">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B602" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C602">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B603" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C603">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B604" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C604">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B605" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C605">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B606" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C606">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B607" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C607">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B608" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C608">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B609" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C609">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B610" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C610">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>https://example.com/images/kuriftu-water-park.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B611" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C611">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>https://example.com/images/kuriftu-water-park-1.jpg</v>
+        <v>https://example.com/images/kuriftu-water-park.jpg</v>
       </c>
       <c r="B612" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C612">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>https://example.com/images/kuriftu-water-park-2.jpg</v>
+        <v>https://example.com/images/kuriftu-water-park-1.jpg</v>
       </c>
       <c r="B613" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C613">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
+        <v>https://example.com/images/kuriftu-water-park-2.jpg</v>
       </c>
       <c r="B614" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C614">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B615" t="str">
         <v>src/Data/resort.tsx</v>
@@ -7166,970 +7166,970 @@
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B616" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C616">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B617" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C617">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B618" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C618">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B619" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C619">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B620" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C620">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B621" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C621">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B622" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C622">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B623" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C623">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B624" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C624">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B625" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C625">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B626" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C626">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B627" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C627">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B628" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C628">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B629" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C629">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B630" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C630">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B631" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C631">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>https://example.com/images/kuriftu-lake-tana.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B632" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C632">
-        <v>355</v>
+        <v>347</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>https://example.com/images/kuriftu-lake-tana-1.jpg</v>
+        <v>https://example.com/images/kuriftu-lake-tana.jpg</v>
       </c>
       <c r="B633" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C633">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>https://example.com/images/kuriftu-lake-tana-2.jpg</v>
+        <v>https://example.com/images/kuriftu-lake-tana-1.jpg</v>
       </c>
       <c r="B634" t="str">
         <v>src/Data/resort.tsx</v>
       </c>
       <c r="C634">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>/images/horizontalCarousel/1.webp</v>
+        <v>https://example.com/images/kuriftu-lake-tana-2.jpg</v>
       </c>
       <c r="B635" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C635">
-        <v>2</v>
+        <v>362</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>/images/horizontalCarousel/2.webp</v>
+        <v>/images/horizontalCarousel/1.webp</v>
       </c>
       <c r="B636" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C636">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>/images/horizontalCarousel/3.webp</v>
+        <v>/images/horizontalCarousel/2.webp</v>
       </c>
       <c r="B637" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C637">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>/images/horizontalCarousel/4.webp</v>
+        <v>/images/horizontalCarousel/3.webp</v>
       </c>
       <c r="B638" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C638">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>/images/horizontalCarousel/5.webp</v>
+        <v>/images/horizontalCarousel/4.webp</v>
       </c>
       <c r="B639" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C639">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>/images/horizontalCarousel/6.webp</v>
+        <v>/images/horizontalCarousel/5.webp</v>
       </c>
       <c r="B640" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C640">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>/images/horizontalCarousel/7.webp</v>
+        <v>/images/horizontalCarousel/6.webp</v>
       </c>
       <c r="B641" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C641">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>/images/experience/1.webp</v>
+        <v>/images/horizontalCarousel/7.webp</v>
       </c>
       <c r="B642" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C642">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>/images/experience/2.webp</v>
+        <v>/images/experience/1.webp</v>
       </c>
       <c r="B643" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C643">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>/images/experience/3.webp</v>
+        <v>/images/experience/2.webp</v>
       </c>
       <c r="B644" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C644">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>/images/experience/4.webp</v>
+        <v>/images/experience/3.webp</v>
       </c>
       <c r="B645" t="str">
         <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C645">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>https://m.media-amazon.com/images/I/717KjgwGLXL._AC_SL1300_.jpg</v>
+        <v>/images/experience/4.webp</v>
       </c>
       <c r="B646" t="str">
-        <v>src/Data/gallery_items.tsx</v>
+        <v>src/Data/horizontalCarousel.tsx</v>
       </c>
       <c r="C646">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>https://m.media-amazon.com/images/I/61306vHf8+L._UF1000,1000_QL80_.jpg</v>
+        <v>https://m.media-amazon.com/images/I/717KjgwGLXL._AC_SL1300_.jpg</v>
       </c>
       <c r="B647" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C647">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>https://pisces.bbystatic.com/image2/BestBuy_US/images/products/1585/15859171_sa.jpg</v>
+        <v>https://m.media-amazon.com/images/I/61306vHf8+L._UF1000,1000_QL80_.jpg</v>
       </c>
       <c r="B648" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C648">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>https://assets.classicfm.com/2021/50/tchaikovsky-1639562612-editorial-long-form-0.jpg</v>
+        <v>https://pisces.bbystatic.com/image2/BestBuy_US/images/products/1585/15859171_sa.jpg</v>
       </c>
       <c r="B649" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C649">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>https://i.ytimg.com/vi/4VZaHs_YCYk/hq720.jpg</v>
+        <v>https://assets.classicfm.com/2021/50/tchaikovsky-1639562612-editorial-long-form-0.jpg</v>
       </c>
       <c r="B650" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C650">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>https://m.media-amazon.com/images/I/81qaC0JI-+L._UF894,1000_QL80_.jpg</v>
+        <v>https://i.ytimg.com/vi/4VZaHs_YCYk/hq720.jpg</v>
       </c>
       <c r="B651" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C651">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>https://www.pianorarescores.com/wp-content/uploads/2014/10/Aram-Khachaturian.jpg</v>
+        <v>https://m.media-amazon.com/images/I/81qaC0JI-+L._UF894,1000_QL80_.jpg</v>
       </c>
       <c r="B652" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C652">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>https://m.media-amazon.com/images/I/81aNPF8YXwL._SL1500_.jpg</v>
+        <v>https://www.pianorarescores.com/wp-content/uploads/2014/10/Aram-Khachaturian.jpg</v>
       </c>
       <c r="B653" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C653">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>https://m.media-amazon.com/images/I/81xJdy0NcBL._SL1500_.jpg</v>
+        <v>https://m.media-amazon.com/images/I/81aNPF8YXwL._SL1500_.jpg</v>
       </c>
       <c r="B654" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C654">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/4/46/Adolphe-Adam-by-Nicolas-Eustache-Maurin.jpg</v>
+        <v>https://m.media-amazon.com/images/I/81xJdy0NcBL._SL1500_.jpg</v>
       </c>
       <c r="B655" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C655">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>https://m.media-amazon.com/images/I/91se4rNs9wL._SL1500_.jpg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/46/Adolphe-Adam-by-Nicolas-Eustache-Maurin.jpg</v>
       </c>
       <c r="B656" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C656">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>https://mf.b37mrtl.ru/rbthmedia/images/2020.09/original/5f4e649f15e9f932270ee462.jpg</v>
+        <v>https://m.media-amazon.com/images/I/91se4rNs9wL._SL1500_.jpg</v>
       </c>
       <c r="B657" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C657">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8315.jpg</v>
+        <v>https://mf.b37mrtl.ru/rbthmedia/images/2020.09/original/5f4e649f15e9f932270ee462.jpg</v>
       </c>
       <c r="B658" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C658">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8532.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8315.jpg</v>
       </c>
       <c r="B659" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C659">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8532.jpg</v>
       </c>
       <c r="B660" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C660">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC9173.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
       </c>
       <c r="B661" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C661">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC9173.jpg</v>
       </c>
       <c r="B662" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C662">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8105.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
       </c>
       <c r="B663" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C663">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-50.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8105.jpg</v>
       </c>
       <c r="B664" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C664">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-76.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-50.jpg</v>
       </c>
       <c r="B665" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C665">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-16.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-76.jpg</v>
       </c>
       <c r="B666" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C666">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-16.jpg</v>
       </c>
       <c r="B667" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C667">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-79.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B668" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C668">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-24.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-79.jpg</v>
       </c>
       <c r="B669" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C669">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/page_media/landing/BOSTON_DAY_SPA__PIER_5_STUDIOS_OCT-13.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-24.jpg</v>
       </c>
       <c r="B670" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C670">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/page_media/landing/IMG_9739.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/page_media/landing/BOSTON_DAY_SPA__PIER_5_STUDIOS_OCT-13.jpg</v>
       </c>
       <c r="B671" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C671">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/page_media/landing/IMG_9741.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/page_media/landing/IMG_9739.jpg</v>
       </c>
       <c r="B672" t="str">
         <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C672">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>https://kurifturesorts.com/images/rooms/deluxe_standard_king.jpg</v>
+        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/page_media/landing/IMG_9741.jpg</v>
       </c>
       <c r="B673" t="str">
-        <v>src/Data/accommodations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C673">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>https://kurifturesorts.com/images/rooms/village_deluxe_king.jpg</v>
+        <v>https://kurifturesorts.com/images/rooms/deluxe_standard_king.jpg</v>
       </c>
       <c r="B674" t="str">
         <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C674">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>https://kurifturesorts.com/images/rooms/village_deluxe_twin.jpg</v>
+        <v>https://kurifturesorts.com/images/rooms/village_deluxe_king.jpg</v>
       </c>
       <c r="B675" t="str">
         <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C675">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>https://kurifturesorts.com/images/rooms/forest_view_king.jpg</v>
+        <v>https://kurifturesorts.com/images/rooms/village_deluxe_twin.jpg</v>
       </c>
       <c r="B676" t="str">
         <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C676">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>https://kurifturesorts.com/images/rooms/forest_view_twin.jpg</v>
+        <v>https://kurifturesorts.com/images/rooms/forest_view_king.jpg</v>
       </c>
       <c r="B677" t="str">
         <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C677">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>https://kurifturesorts.com/images/awash/premium_suite.jpg</v>
+        <v>https://kurifturesorts.com/images/rooms/forest_view_twin.jpg</v>
       </c>
       <c r="B678" t="str">
         <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C678">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>https://kurifturesorts.com/images/awash/junior_suite.jpg</v>
+        <v>https://kurifturesorts.com/images/awash/premium_suite.jpg</v>
       </c>
       <c r="B679" t="str">
         <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C679">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>https://kurifturesorts.com/images/awash/executive_suite.jpg</v>
+        <v>https://kurifturesorts.com/images/awash/junior_suite.jpg</v>
       </c>
       <c r="B680" t="str">
         <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C680">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>https://kurifturesorts.com/images/awash/presidential_suite.jpg</v>
+        <v>https://kurifturesorts.com/images/awash/executive_suite.jpg</v>
       </c>
       <c r="B681" t="str">
         <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C681">
-        <v>160</v>
+        <v>135</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
+        <v>https://kurifturesorts.com/images/awash/presidential_suite.jpg</v>
       </c>
       <c r="B682" t="str">
-        <v>src/Data/MockData.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C682">
-        <v>12</v>
+        <v>160</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B683" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C683">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B684" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C684">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B685" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C685">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B686" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C686">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B687" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C687">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B688" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C688">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B689" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C689">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B690" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C690">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B691" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C691">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B692" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C692">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B693" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C693">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B694" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C694">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B695" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C695">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B696" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C696">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B697" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C697">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B698" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C698">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B699" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C699">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B700" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C700">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu-1.jpg</v>
+        <v>https://example.com/images/kuriftu-bishoftu.jpg</v>
       </c>
       <c r="B701" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C701">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu-2.jpg</v>
+        <v>https://example.com/images/kuriftu-bishoftu-1.jpg</v>
       </c>
       <c r="B702" t="str">
         <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C702">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>/home/homeVideo.mov</v>
+        <v>https://example.com/images/kuriftu-bishoftu-2.jpg</v>
       </c>
       <c r="B703" t="str">
-        <v>src/Routes/landing.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C703">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="704">

--- a/media_references.xlsx
+++ b/media_references.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C715"/>
+  <dimension ref="A1:C499"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,7 +418,7 @@
         <v>src/components/RoomModal.tsx</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -445,1693 +445,1693 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>/home/homeVideo.mov</v>
+        <v>https://kurifturesorts.com/_nuxt/img/mass.bb8baa5.webp</v>
       </c>
       <c r="B5" t="str">
-        <v>src/Routes/landing.tsx</v>
+        <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.54a7799.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/openWindow.5839f5b.webp</v>
       </c>
       <c r="B6" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.99dded0.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.975870d.webp</v>
       </c>
       <c r="B7" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.6dced12.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wellness.bd707c7.webp</v>
       </c>
       <c r="B8" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.9d46069.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.975870d.webp</v>
       </c>
       <c r="B9" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C9">
-        <v>13</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fit.47db4b5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2L.91c45e9.webp</v>
       </c>
       <c r="B10" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C10">
-        <v>20</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wide.735b796.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/well.fcab3b9.webp</v>
       </c>
       <c r="B11" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C11">
-        <v>24</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.578008f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.1b81bb4.webp</v>
       </c>
       <c r="B12" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C12">
-        <v>25</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.5f86ac3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.02cca05.webp</v>
       </c>
       <c r="B13" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C13">
-        <v>26</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.083e652.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.33fc8c3.webp</v>
       </c>
       <c r="B14" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C14">
-        <v>64</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.07e7d88.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/5.f39e554.webp</v>
       </c>
       <c r="B15" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C15">
-        <v>65</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/mass.bb8baa5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/well2.82034ac.webp</v>
       </c>
       <c r="B16" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C16">
-        <v>69</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/openWindow.5839f5b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long1.9fafbdc.webp</v>
       </c>
       <c r="B17" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C17">
-        <v>70</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.f34a4ea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.5a8bb06.webp</v>
       </c>
       <c r="B18" t="str">
         <v>src/MockData/wellness.tsx</v>
       </c>
       <c r="C18">
-        <v>71</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.975870d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterhouseLong.48262ff.webp</v>
       </c>
       <c r="B19" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C19">
-        <v>110</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wellness.bd707c7.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterhouseLong.48262ff.webp</v>
       </c>
       <c r="B20" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C20">
-        <v>111</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.975870d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wavepoolLong.5549e3f.webp</v>
       </c>
       <c r="B21" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C21">
-        <v>116</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2L.91c45e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SpiralSlideLong.9db3edb.webp</v>
       </c>
       <c r="B22" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C22">
-        <v>117</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/well.fcab3b9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/boomLong.81f1304.webp</v>
       </c>
       <c r="B23" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C23">
-        <v>118</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.1b81bb4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/FikatCircusLong.c96ffbc.webp</v>
       </c>
       <c r="B24" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C24">
-        <v>155</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.02cca05.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GiftshopLong.008270b.webp</v>
       </c>
       <c r="B25" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C25">
-        <v>156</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.33fc8c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/exp1.d4c3656.webp</v>
       </c>
       <c r="B26" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C26">
-        <v>157</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/5.f39e554.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/exp2.9bf24be.webp</v>
       </c>
       <c r="B27" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C27">
-        <v>158</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/well2.82034ac.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/exp3.f02533c.webp</v>
       </c>
       <c r="B28" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/waterParkHomeData.tsx</v>
       </c>
       <c r="C28">
-        <v>162</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long1.9fafbdc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Glamping.75aadd4.webp</v>
       </c>
       <c r="B29" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/room.tsx</v>
       </c>
       <c r="C29">
-        <v>163</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.5a8bb06.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
       </c>
       <c r="B30" t="str">
-        <v>src/MockData/wellness.tsx</v>
+        <v>src/MockData/room.tsx</v>
       </c>
       <c r="C30">
-        <v>164</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterhouseLong.48262ff.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_spa1.webp</v>
       </c>
       <c r="B31" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/room.tsx</v>
       </c>
       <c r="C31">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterhouseLong.48262ff.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_premium_suite.webp</v>
       </c>
       <c r="B32" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/room.tsx</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wavepoolLong.5549e3f.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_junior_suite.webp</v>
       </c>
       <c r="B33" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/room.tsx</v>
       </c>
       <c r="C33">
-        <v>26</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SpiralSlideLong.9db3edb.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_executive_suite.webp</v>
       </c>
       <c r="B34" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/room.tsx</v>
       </c>
       <c r="C34">
-        <v>32</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/boomLong.81f1304.webp</v>
+        <v>https://www.kurifturesorts.com/_nuxt/img/awash_presidential_suite.webp</v>
       </c>
       <c r="B35" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/room.tsx</v>
       </c>
       <c r="C35">
-        <v>38</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/FikatCircusLong.c96ffbc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.46e7606.webp</v>
       </c>
       <c r="B36" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/room.tsx</v>
       </c>
       <c r="C36">
-        <v>44</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GiftshopLong.008270b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/acc.21e7f6a.webp</v>
       </c>
       <c r="B37" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/resortsDetails.tsx</v>
       </c>
       <c r="C37">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp1.d4c3656.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B38" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C38">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp2.9bf24be.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B39" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C39">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp3.f02533c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B40" t="str">
-        <v>src/MockData/waterParkHomeData.tsx</v>
+        <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C40">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.75aadd4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B41" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/resortsAll.tsx</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Tana.303f00c.webp</v>
       </c>
       <c r="B42" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/reservationRooms.tsx</v>
       </c>
       <c r="C42">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_spa1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/FeaturedStory.6dcf1a8.webp</v>
       </c>
       <c r="B43" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/landingPage.tsx</v>
       </c>
       <c r="C43">
-        <v>21</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_premium_suite.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6474ed2.jpg</v>
       </c>
       <c r="B44" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/giftVoucher.tsx</v>
       </c>
       <c r="C44">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_junior_suite.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.cba30ab.webp</v>
       </c>
       <c r="B45" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C45">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_executive_suite.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.d4feaba.webp</v>
       </c>
       <c r="B46" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C46">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/awash_presidential_suite.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
       </c>
       <c r="B47" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C47">
-        <v>109</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.46e7606.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.33fc8c3.webp</v>
       </c>
       <c r="B48" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C48">
-        <v>135</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>/africanvillage/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/5.9fafbdc.webp</v>
       </c>
       <c r="B49" t="str">
-        <v>src/MockData/room.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C49">
-        <v>140</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>/entoto/entato1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun1.6e87593.webp</v>
       </c>
       <c r="B50" t="str">
-        <v>src/MockData/resortsDetails.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C50">
-        <v>16</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>/entoto/entoto.mov</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.1b81bb4.webp</v>
       </c>
       <c r="B51" t="str">
-        <v>src/MockData/resortsDetails.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C51">
-        <v>17</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishAcc.1bbca14.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/waterpark2.7574045.jpg</v>
       </c>
       <c r="B52" t="str">
-        <v>src/MockData/resortsDetails.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C52">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>/bishoftu/bishoftu.mov</v>
+        <v>https://kurifturesorts.com/_nuxt/img/kuriftu%20dec%2022-5422-min%20(1).e20e04c.jpg</v>
       </c>
       <c r="B53" t="str">
-        <v>src/MockData/resortsDetails.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C53">
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/acc.21e7f6a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide2.ca27dc6.webp</v>
       </c>
       <c r="B54" t="str">
-        <v>src/MockData/resortsDetails.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C54">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Accomodation1.c444805.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.ed0beaf.webp</v>
       </c>
       <c r="B55" t="str">
-        <v>src/MockData/resortsDetails.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C55">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>/africanvillage/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/_DSC5820%20(2)-min.c7b8704.jpg</v>
       </c>
       <c r="B56" t="str">
-        <v>src/MockData/resortsDetails.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C56">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>/africanvillage/africanVillage.MOV</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TreatByThePorch.df2143d.webp</v>
       </c>
       <c r="B57" t="str">
-        <v>src/MockData/resortsDetails.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C57">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-49.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide5.e0dfde1.webp</v>
       </c>
       <c r="B58" t="str">
-        <v>src/MockData/resortsAll.tsx</v>
+        <v>src/MockData/gallery.tsx</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.8b94d4d.webp</v>
       </c>
       <c r="B59" t="str">
-        <v>src/MockData/resortsAll.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C59">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Swimming2.c58b523.webp</v>
       </c>
       <c r="B60" t="str">
-        <v>src/MockData/resortsAll.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C60">
-        <v>29</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Kayaking.8a09cfa.webp</v>
       </c>
       <c r="B61" t="str">
-        <v>src/MockData/resortsAll.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C61">
-        <v>38</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkF.48a36af.webp</v>
       </c>
       <c r="B62" t="str">
-        <v>src/MockData/resortsAll.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C62">
-        <v>47</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TripToTheFalls.ffa9182.webp</v>
       </c>
       <c r="B63" t="str">
-        <v>src/MockData/resortsAll.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C63">
-        <v>56</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>/africanvillage/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
       </c>
       <c r="B64" t="str">
-        <v>src/MockData/reservationRooms.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C64">
-        <v>13</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.46e7606.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CabanaDinig.3d6bf71.webp</v>
       </c>
       <c r="B65" t="str">
-        <v>src/MockData/reservationRooms.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C65">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.75aadd4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/BoatRide.9d78045.webp</v>
       </c>
       <c r="B66" t="str">
-        <v>src/MockData/reservationRooms.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C66">
-        <v>33</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Tana.303f00c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
       </c>
       <c r="B67" t="str">
-        <v>src/MockData/reservationRooms.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C67">
-        <v>43</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Adventure.bb2f8d1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CabanaDinigLong.f713425.webp</v>
       </c>
       <c r="B68" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C68">
-        <v>13</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Catering.8818461.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SwimmingPoolLong.3075d7d.webp</v>
       </c>
       <c r="B69" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C69">
-        <v>23</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Adventure.bb2f8d1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching1.15a4456.webp</v>
       </c>
       <c r="B70" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C70">
-        <v>35</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.e6ec880.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TripToTheFalls.ffa9182.webp</v>
       </c>
       <c r="B71" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C71">
-        <v>45</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Kuriftu%20Construction.56c04b5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Experience.0da9d1f.webp</v>
       </c>
       <c r="B72" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C72">
-        <v>56</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Waterpark.0b8de07.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/awash-cover.8aba739.webp</v>
       </c>
       <c r="B73" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C73">
-        <v>68</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Tana.303f00c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CamelRide.3ed74a1.webp</v>
       </c>
       <c r="B74" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C74">
-        <v>78</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/FeaturedStory.6dcf1a8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Yoga.3b1b821.webp</v>
       </c>
       <c r="B75" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C75">
-        <v>89</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>/entoto/entoto.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long3.cd91821.webp</v>
       </c>
       <c r="B76" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C76">
-        <v>101</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>/bishoftu/bishifto1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.1b81bb4.webp</v>
       </c>
       <c r="B77" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/experiences.tsx</v>
       </c>
       <c r="C77">
-        <v>111</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>/boston/boston.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
       </c>
       <c r="B78" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C78">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>/africanvillage/1.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.9e5c587.webp</v>
       </c>
       <c r="B79" t="str">
-        <v>src/MockData/landingPage.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C79">
-        <v>130</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6474ed2.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.30afcb1.webp</v>
       </c>
       <c r="B80" t="str">
-        <v>src/MockData/giftVoucher.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C80">
-        <v>4</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>/entoto/1.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
       </c>
       <c r="B81" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>/entoto/2.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.9e5c587.webp</v>
       </c>
       <c r="B82" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>188</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>/entoto/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.30afcb1.webp</v>
       </c>
       <c r="B83" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>196</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>/entoto/4.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
       </c>
       <c r="B84" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C84">
-        <v>6</v>
+        <v>209</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>/entoto/5.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
       </c>
       <c r="B85" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>210</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>/entoto/6.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Cabana.2f03513.webp</v>
       </c>
       <c r="B86" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C86">
-        <v>8</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>/entoto/7.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
       </c>
       <c r="B87" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C87">
-        <v>9</v>
+        <v>218</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>/entoto/8.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
       </c>
       <c r="B88" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C88">
-        <v>10</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>/entoto/9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
       </c>
       <c r="B89" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C89">
-        <v>11</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>/entoto/10.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
       </c>
       <c r="B90" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C90">
-        <v>12</v>
+        <v>247</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>/entoto/11.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
       </c>
       <c r="B91" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C91">
-        <v>13</v>
+        <v>254</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>/entoto/12.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Cabana.2f03513.webp</v>
       </c>
       <c r="B92" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C92">
-        <v>14</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>/entoto/13.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.0111b85.webp</v>
       </c>
       <c r="B93" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C93">
-        <v>15</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>/entoto/14.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.f4ccdbc.webp</v>
       </c>
       <c r="B94" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C94">
-        <v>16</v>
+        <v>278</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>/entoto/15.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.19a424e.webp</v>
       </c>
       <c r="B95" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C95">
-        <v>17</v>
+        <v>286</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>/entoto/16.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
       </c>
       <c r="B96" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C96">
-        <v>18</v>
+        <v>297</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>/bishoftu/2.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wedding.b762def.webp</v>
       </c>
       <c r="B97" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C97">
-        <v>22</v>
+        <v>303</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>/bishoftu/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Birthdays.cd4c5d2.webp</v>
       </c>
       <c r="B98" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C98">
-        <v>23</v>
+        <v>313</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>/bishoftu/4.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SocialEvents.8fadfab.webp</v>
       </c>
       <c r="B99" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C99">
-        <v>24</v>
+        <v>323</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>/bishoftu/5.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
       </c>
       <c r="B100" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C100">
-        <v>25</v>
+        <v>342</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>/bishoftu/6.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
       </c>
       <c r="B101" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C101">
-        <v>26</v>
+        <v>343</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>/bishoftu/7.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s3.38a710c.webp</v>
       </c>
       <c r="B102" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C102">
-        <v>27</v>
+        <v>344</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>/bishoftu/8.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.628f404.webp</v>
       </c>
       <c r="B103" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C103">
-        <v>28</v>
+        <v>352</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>/bishoftu/10.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
       </c>
       <c r="B104" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C104">
-        <v>29</v>
+        <v>360</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>/bishoftu/11.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
       </c>
       <c r="B105" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C105">
-        <v>30</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>/bishoftu/12.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/we.c516b54.webp</v>
       </c>
       <c r="B106" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C106">
-        <v>31</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>/bishoftu/13.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
       </c>
       <c r="B107" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C107">
-        <v>32</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>/bishoftu/14.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
       </c>
       <c r="B108" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C108">
-        <v>33</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>/bishoftu/15.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.628f404.webp</v>
       </c>
       <c r="B109" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C109">
-        <v>34</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
       </c>
       <c r="B110" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C110">
-        <v>38</v>
+        <v>387</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
       </c>
       <c r="B111" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C111">
-        <v>39</v>
+        <v>388</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
       </c>
       <c r="B112" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C112">
-        <v>40</v>
+        <v>389</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching.75afd69.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e579177.webp</v>
       </c>
       <c r="B113" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C113">
-        <v>41</v>
+        <v>397</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
       </c>
       <c r="B114" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C114">
-        <v>43</v>
+        <v>405</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.cba30ab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
       </c>
       <c r="B115" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C115">
-        <v>46</v>
+        <v>413</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.d4feaba.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingLong.07f0acc.webp</v>
       </c>
       <c r="B116" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C116">
-        <v>47</v>
+        <v>417</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
       </c>
       <c r="B117" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C117">
-        <v>48</v>
+        <v>418</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.33fc8c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
       </c>
       <c r="B118" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C118">
-        <v>49</v>
+        <v>419</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/5.9fafbdc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.b4fafda.webp</v>
       </c>
       <c r="B119" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C119">
-        <v>50</v>
+        <v>420</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun1.6e87593.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
       </c>
       <c r="B120" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C120">
-        <v>51</v>
+        <v>432</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.1b81bb4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
       </c>
       <c r="B121" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C121">
-        <v>52</v>
+        <v>433</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>/africanvillage/1.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e579177.webp</v>
       </c>
       <c r="B122" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C122">
-        <v>55</v>
+        <v>441</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>/africanvillage/2.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
       </c>
       <c r="B123" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C123">
-        <v>56</v>
+        <v>449</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>/africanvillage/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
       </c>
       <c r="B124" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C124">
-        <v>57</v>
+        <v>457</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/_DSC5641%20(2)-min.f32edfd.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.b4fafda.webp</v>
       </c>
       <c r="B125" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C125">
-        <v>60</v>
+        <v>461</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/waterpark2.7574045.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingLong.07f0acc.webp</v>
       </c>
       <c r="B126" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C126">
-        <v>61</v>
+        <v>462</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/kuriftu%20dec%2022-5391-min%20(1).5f30be4.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
       </c>
       <c r="B127" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C127">
-        <v>62</v>
+        <v>463</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/kuriftu%20dec%2022-5422-min%20(1).e20e04c.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
       </c>
       <c r="B128" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C128">
-        <v>63</v>
+        <v>464</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide2.ca27dc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
       </c>
       <c r="B129" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C129">
-        <v>64</v>
+        <v>474</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.ed0beaf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e3ecdac.webp</v>
       </c>
       <c r="B130" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C130">
-        <v>65</v>
+        <v>481</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/_DSC5820%20(2)-min.c7b8704.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
       </c>
       <c r="B131" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C131">
-        <v>66</v>
+        <v>489</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TreatByThePorch.df2143d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
       </c>
       <c r="B132" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C132">
-        <v>67</v>
+        <v>497</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide5.e0dfde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Mels.d221dee.webp</v>
       </c>
       <c r="B133" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C133">
-        <v>68</v>
+        <v>503</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>/boston/1.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wedding1.4c034c6.webp</v>
       </c>
       <c r="B134" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C134">
-        <v>71</v>
+        <v>510</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>/boston/2.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Honeymoon.c509471.webp</v>
       </c>
       <c r="B135" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C135">
-        <v>72</v>
+        <v>517</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>/boston/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/7.2dae83c.webp</v>
       </c>
       <c r="B136" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C136">
-        <v>73</v>
+        <v>521</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>/boston/4.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/10.60d29d1.webp</v>
       </c>
       <c r="B137" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C137">
-        <v>74</v>
+        <v>522</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>/boston/5.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.726df95.webp</v>
       </c>
       <c r="B138" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C138">
-        <v>75</v>
+        <v>523</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>/boston/6.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.cba30ab.webp</v>
       </c>
       <c r="B139" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C139">
-        <v>76</v>
+        <v>524</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>/boston/7.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.b337c8c.webp</v>
       </c>
       <c r="B140" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/events.tsx</v>
       </c>
       <c r="C140">
-        <v>77</v>
+        <v>525</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>/boston/8.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
       </c>
       <c r="B141" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C141">
-        <v>78</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>/boston/9.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
       </c>
       <c r="B142" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C142">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/24.9dfafe2.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
       </c>
       <c r="B143" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/eventPageData.tsx</v>
       </c>
       <c r="C143">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/25.458bb05.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
       </c>
       <c r="B144" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C144">
-        <v>81</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/26.a81e8e3.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
       </c>
       <c r="B145" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C145">
-        <v>82</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/27.cc2beb9.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
       </c>
       <c r="B146" t="str">
-        <v>src/MockData/gallery.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C146">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp3.fe1f858.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
       </c>
       <c r="B147" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C147">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp.0810993.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheRidersRanch.2035096.webp</v>
       </c>
       <c r="B148" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C148">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/exp2.a0ae964.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CastelBar&amp;Grill.1f72ad2.webp</v>
       </c>
       <c r="B149" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C149">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.8b94d4d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheMarksmanBar&amp;Grill.0af1692.webp</v>
       </c>
       <c r="B150" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C150">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>/entoto/10.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/PitStopBar&amp;Grill.d7a6bea.webp</v>
       </c>
       <c r="B151" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C151">
-        <v>26</v>
+        <v>53</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.82d1f76.webp</v>
       </c>
       <c r="B152" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C152">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fe3.89f2a9f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeFront.55a2ad2.webp</v>
       </c>
       <c r="B153" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C153">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>/entoto/bbq.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Lequanda.9dcb7ac.webp</v>
       </c>
       <c r="B154" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C154">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/feature.7383491.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkCabanas.00f0dde.webp</v>
       </c>
       <c r="B155" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C155">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fe2.8b9e86a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkDiner.e837424.webp</v>
       </c>
       <c r="B156" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C156">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fe3.89f2a9f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Cabbana.911be42.webp</v>
       </c>
       <c r="B157" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C157">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Swimming2.c58b523.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeFrontF.37dd2a9.webp</v>
       </c>
       <c r="B158" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C158">
         <v>77</v>
@@ -2139,6134 +2139,3758 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Kayaking.8a09cfa.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CabbanaF.295b550.webp</v>
       </c>
       <c r="B159" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C159">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkF.48a36af.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LequandaF.73439a0.webp</v>
       </c>
       <c r="B160" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C160">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Kayaking.8a09cfa.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkDinerF.f8a74fa.webp</v>
       </c>
       <c r="B161" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C161">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>/bishoftu/8.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/WaterparkCabanasO.a6a031a.webp</v>
       </c>
       <c r="B162" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C162">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>/bishoftu/3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffetO.ea5b225.webp</v>
       </c>
       <c r="B163" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C163">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Lequanda.ca87f54.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.89ba262.webp</v>
       </c>
       <c r="B164" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C164">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching1.9746917.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
       </c>
       <c r="B165" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C165">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Hiking.ed4cbf4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.7c07513.webp</v>
       </c>
       <c r="B166" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C166">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TripToTheFalls.ffa9182.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.a30d654.webp</v>
       </c>
       <c r="B167" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C167">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.7c07513.webp</v>
       </c>
       <c r="B168" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C168">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CabanaDinig.3d6bf71.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
       </c>
       <c r="B169" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C169">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BoatRide.9d78045.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.89ba262.webp</v>
       </c>
       <c r="B170" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C170">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.a30d654.webp</v>
       </c>
       <c r="B171" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C171">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CabanaDinigLong.f713425.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
       </c>
       <c r="B172" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C172">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SwimmingPoolLong.3075d7d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ThePoolBar&amp;Grill.33fc8c3.webp</v>
       </c>
       <c r="B173" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C173">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/MonastryVisit.5d60dd6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/din1.79ddaae.webp</v>
       </c>
       <c r="B174" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C174">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BirdWatching1.15a4456.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/din2.2a7cebb.webp</v>
       </c>
       <c r="B175" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C175">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TripToTheFalls.ffa9182.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/din3.10849d7.webp</v>
       </c>
       <c r="B176" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C176">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Experience.0da9d1f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
       </c>
       <c r="B177" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C177">
-        <v>208</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre2.7f3adf1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ThePoolBar&amp;Grill.33fc8c3.webp</v>
       </c>
       <c r="B178" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C178">
-        <v>209</v>
+        <v>190</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/awash-cover.8aba739.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide.d5ccc8b.webp</v>
       </c>
       <c r="B179" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C179">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CamelRide.3ed74a1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide2.ca27dc6.webp</v>
       </c>
       <c r="B180" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C180">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CamelRide.3ed74a1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide3.7e0fcf3.webp</v>
       </c>
       <c r="B181" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C181">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/fe3.89f2a9f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide4.8b1e6bb.webp</v>
       </c>
       <c r="B182" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C182">
-        <v>233</v>
+        <v>205</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Yoga.3b1b821.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide5.e0dfde1.webp</v>
       </c>
       <c r="B183" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C183">
-        <v>239</v>
+        <v>206</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long3.cd91821.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/dinslide6.d93b9ac.webp</v>
       </c>
       <c r="B184" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C184">
-        <v>245</v>
+        <v>207</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>/spa/spa3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Plaza.a45b650.webp</v>
       </c>
       <c r="B185" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C185">
-        <v>251</v>
+        <v>214</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/PrivateEvent.6edee64.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.ed0beaf.webp</v>
       </c>
       <c r="B186" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C186">
-        <v>257</v>
+        <v>223</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/BreakfastInTheDesert.bcdd2cd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TreatByThePorch.df2143d.webp</v>
       </c>
       <c r="B187" t="str">
-        <v>src/MockData/experiences.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C187">
-        <v>264</v>
+        <v>229</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ReserveATable.b368639.webp</v>
       </c>
       <c r="B188" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/dining.tsx</v>
       </c>
       <c r="C188">
-        <v>10</v>
+        <v>235</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/contact.2e8edc6.jpg</v>
       </c>
       <c r="B189" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/contactUsData.tsx</v>
       </c>
       <c r="C189">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s3.38a710c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s5.52f7de0.webp</v>
       </c>
       <c r="B190" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C190">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
       </c>
       <c r="B191" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C191">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>/entoto/8.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
       </c>
       <c r="B192" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C192">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Birthday.3362d09.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
       </c>
       <c r="B193" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C193">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SocialEvent.f486a56.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/re.0af1692.webp</v>
       </c>
       <c r="B194" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C194">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingVenue.4c9426b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/conf.5532829.webp</v>
       </c>
       <c r="B195" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C195">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Open%20Air.4abd236.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/MultiPurposeCabin.8dde207.webp</v>
       </c>
       <c r="B196" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C196">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/InDoor.4253f5a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
       </c>
       <c r="B197" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C197">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/TheRidersRanch.2035096.webp</v>
       </c>
       <c r="B198" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C198">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.9e5c587.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CastelBar&amp;Grill.1f72ad2.webp</v>
       </c>
       <c r="B199" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C199">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.30afcb1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
       </c>
       <c r="B200" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C200">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.a740033.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SpaceOrganization.d5320f2.webp</v>
       </c>
       <c r="B201" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C201">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ClosingEvent.dee1570.webp</v>
       </c>
       <c r="B202" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C202">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/waterpark.9066e15.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
       </c>
       <c r="B203" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C203">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
       </c>
       <c r="B204" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C204">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/catering.9294532.webp</v>
       </c>
       <c r="B205" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C205">
-        <v>106</v>
+        <v>185</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.0cf4a1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1O.5433205.webp</v>
       </c>
       <c r="B206" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C206">
-        <v>107</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>https://www.kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2O.754ae7c.webp</v>
       </c>
       <c r="B207" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C207">
-        <v>114</v>
+        <v>199</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
       </c>
       <c r="B208" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C208">
-        <v>124</v>
+        <v>212</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/concert.e1cdbcd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
       </c>
       <c r="B209" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C209">
-        <v>133</v>
+        <v>213</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/social.c5ddebd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateRetreat.3b7233d.webp</v>
       </c>
       <c r="B210" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C210">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
       </c>
       <c r="B211" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C211">
-        <v>153</v>
+        <v>222</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.a740033.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
       </c>
       <c r="B212" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C212">
-        <v>160</v>
+        <v>233</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Cabbana.911be42.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateRetreat.3b7233d.webp</v>
       </c>
       <c r="B213" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C213">
-        <v>167</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/waterpark.9066e15.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
       </c>
       <c r="B214" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C214">
-        <v>173</v>
+        <v>254</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
       </c>
       <c r="B215" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C215">
-        <v>182</v>
+        <v>262</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.9e5c587.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
       </c>
       <c r="B216" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C216">
-        <v>190</v>
+        <v>270</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.30afcb1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
       </c>
       <c r="B217" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C217">
-        <v>198</v>
+        <v>278</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/co.e67c272.webp</v>
       </c>
       <c r="B218" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C218">
-        <v>211</v>
+        <v>291</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/co2.c47cb91.webp</v>
       </c>
       <c r="B219" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C219">
-        <v>212</v>
+        <v>292</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Cabana.2f03513.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Co3.931a172.webp</v>
       </c>
       <c r="B220" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C220">
-        <v>213</v>
+        <v>299</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/co2.c47cb91.webp</v>
       </c>
       <c r="B221" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C221">
-        <v>220</v>
+        <v>309</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bd.654e148.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/co.e67c272.webp</v>
       </c>
       <c r="B222" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C222">
-        <v>230</v>
+        <v>319</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/soci.76a5a73.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.1e370ba.webp</v>
       </c>
       <c r="B223" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C223">
-        <v>239</v>
+        <v>330</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SpaceOrganization.4284dbb.webp</v>
       </c>
       <c r="B224" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C224">
-        <v>249</v>
+        <v>338</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ClosingEvent.1e10bb5.webp</v>
       </c>
       <c r="B225" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/celebrationsAndEvent.tsx</v>
       </c>
       <c r="C225">
-        <v>256</v>
+        <v>345</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Cabana.2f03513.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/ArtGallery.cb59c6c.webp</v>
       </c>
       <c r="B226" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C226">
-        <v>263</v>
+        <v>13</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.0111b85.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/SteamSaunaJaccuzi.644ea57.webp</v>
       </c>
       <c r="B227" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/bostonHomeData.tsx</v>
       </c>
       <c r="C227">
-        <v>272</v>
+        <v>32</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EventConsulting.f4ccdbc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/AfricaRoomBed.28e54c2.jpg</v>
       </c>
       <c r="B228" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/africanVillageAccomodation.tsx</v>
       </c>
       <c r="C228">
-        <v>280</v>
+        <v>30</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Entertainment.19a424e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/AfricaRestaurant.36863f2.jpg</v>
       </c>
       <c r="B229" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/africanVillageAccomodation.tsx</v>
       </c>
       <c r="C229">
-        <v>288</v>
+        <v>40</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/AfricaMassage.ff8ac7b.jpg</v>
       </c>
       <c r="B230" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/africanVillageAccomodation.tsx</v>
       </c>
       <c r="C230">
-        <v>299</v>
+        <v>49</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wedding.b762def.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2bb9fd7.webp</v>
       </c>
       <c r="B231" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C231">
-        <v>305</v>
+        <v>9</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Birthdays.cd4c5d2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.609dbb9.webp</v>
       </c>
       <c r="B232" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C232">
-        <v>315</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SocialEvents.8fadfab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.89f1f99.webp</v>
       </c>
       <c r="B233" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C233">
-        <v>325</v>
+        <v>11</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/hors.1e1048c.webp</v>
       </c>
       <c r="B234" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C234">
-        <v>344</v>
+        <v>19</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/zip.c6c6a45.webp</v>
       </c>
       <c r="B235" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C235">
-        <v>345</v>
+        <v>26</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s3.38a710c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/play.54f31e5.webp</v>
       </c>
       <c r="B236" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/adventure.tsx</v>
       </c>
       <c r="C236">
-        <v>346</v>
+        <v>33</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.628f404.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
       </c>
       <c r="B237" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C237">
-        <v>354</v>
+        <v>20</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B238" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C238">
-        <v>362</v>
+        <v>36</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
       </c>
       <c r="B239" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C239">
-        <v>370</v>
+        <v>45</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/we.c516b54.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.1424c84.webp</v>
       </c>
       <c r="B240" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C240">
-        <v>374</v>
+        <v>54</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.5c6074e.webp</v>
       </c>
       <c r="B241" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C241">
-        <v>375</v>
+        <v>64</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B242" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C242">
-        <v>376</v>
+        <v>81</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.628f404.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
       </c>
       <c r="B243" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C243">
-        <v>377</v>
+        <v>90</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
       </c>
       <c r="B244" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C244">
-        <v>389</v>
+        <v>99</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Premium.eb88e0f.webp</v>
       </c>
       <c r="B245" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C245">
-        <v>390</v>
+        <v>116</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Junior.d5ce7f3.webp</v>
       </c>
       <c r="B246" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C246">
-        <v>391</v>
+        <v>125</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e579177.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Experience.56a6110.webp</v>
       </c>
       <c r="B247" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C247">
-        <v>399</v>
+        <v>134</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.7f3adf1.webp</v>
       </c>
       <c r="B248" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C248">
-        <v>407</v>
+        <v>143</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
       </c>
       <c r="B249" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C249">
-        <v>415</v>
+        <v>181</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingLong.07f0acc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
       </c>
       <c r="B250" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C250">
-        <v>419</v>
+        <v>199</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.64d69d1.webp</v>
       </c>
       <c r="B251" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C251">
-        <v>420</v>
+        <v>200</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.1ea7836.webp</v>
       </c>
       <c r="B252" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C252">
-        <v>421</v>
+        <v>204</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.b4fafda.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.59933f3.webp</v>
       </c>
       <c r="B253" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C253">
-        <v>422</v>
+        <v>205</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wed.2e89f5a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.9e6f0ca.webp</v>
       </c>
       <c r="B254" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C254">
-        <v>434</v>
+        <v>227</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.76bf09d.webp</v>
       </c>
       <c r="B255" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C255">
-        <v>435</v>
+        <v>239</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e579177.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0cc943d.webp</v>
       </c>
       <c r="B256" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C256">
-        <v>443</v>
+        <v>246</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.b0c6e49.webp</v>
       </c>
       <c r="B257" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C257">
-        <v>451</v>
+        <v>247</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.12d11d4.webp</v>
       </c>
       <c r="B258" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C258">
-        <v>459</v>
+        <v>248</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.b4fafda.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.d471ca4.webp</v>
       </c>
       <c r="B259" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C259">
-        <v>463</v>
+        <v>249</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingLong.07f0acc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
       </c>
       <c r="B260" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C260">
-        <v>464</v>
+        <v>269</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WeddingArea.9732696.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
       </c>
       <c r="B261" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C261">
-        <v>465</v>
+        <v>279</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/wedding.2364f4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
       </c>
       <c r="B262" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C262">
-        <v>466</v>
+        <v>287</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.eb2af55.webp</v>
       </c>
       <c r="B263" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C263">
-        <v>476</v>
+        <v>297</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Landscape.e3ecdac.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.fcb2c4b.webp</v>
       </c>
       <c r="B264" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C264">
-        <v>483</v>
+        <v>298</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bridalshower.e90f713.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.95ea902.webp</v>
       </c>
       <c r="B265" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C265">
-        <v>491</v>
+        <v>299</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Bachelorette.92bb38c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.12d11d4.webp</v>
       </c>
       <c r="B266" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C266">
-        <v>499</v>
+        <v>300</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Mels.d221dee.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/gardenLong.f325f95.webp</v>
       </c>
       <c r="B267" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C267">
-        <v>505</v>
+        <v>319</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wedding1.4c034c6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/gardenLong2.a5ba8bc.webp</v>
       </c>
       <c r="B268" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C268">
-        <v>512</v>
+        <v>320</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Honeymoon.c509471.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B269" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C269">
-        <v>519</v>
+        <v>328</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/7.2dae83c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
       </c>
       <c r="B270" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C270">
-        <v>523</v>
+        <v>338</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/10.60d29d1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
       </c>
       <c r="B271" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C271">
-        <v>524</v>
+        <v>346</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.726df95.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.0052dfd.webp</v>
       </c>
       <c r="B272" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C272">
-        <v>525</v>
+        <v>356</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.cba30ab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.2faa8da.webp</v>
       </c>
       <c r="B273" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C273">
-        <v>526</v>
+        <v>357</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.b337c8c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.8096683.webp</v>
       </c>
       <c r="B274" t="str">
-        <v>src/MockData/events.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C274">
-        <v>527</v>
+        <v>358</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.0a26366.webp</v>
       </c>
       <c r="B275" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C275">
-        <v>5</v>
+        <v>359</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long1.f233b2e.webp</v>
       </c>
       <c r="B276" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C276">
-        <v>6</v>
+        <v>380</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeSide.01bf8ea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.d8e3c85.webp</v>
       </c>
       <c r="B277" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C277">
-        <v>7</v>
+        <v>381</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0a370e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B278" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C278">
-        <v>8</v>
+        <v>387</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>/images/event.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
       </c>
       <c r="B279" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C279">
-        <v>10</v>
+        <v>396</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>/spa/spa1.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
       </c>
       <c r="B280" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C280">
-        <v>17</v>
+        <v>405</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>/spa/spa2.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.020c051.webp</v>
       </c>
       <c r="B281" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C281">
-        <v>26</v>
+        <v>415</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>/spa/spa3.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Presidential.5c6074e.webp</v>
       </c>
       <c r="B282" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C282">
-        <v>36</v>
+        <v>416</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>/spa/spa4.JPG</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.65258bc.webp</v>
       </c>
       <c r="B283" t="str">
-        <v>src/MockData/eventPageData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C283">
-        <v>45</v>
+        <v>417</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.6510504.webp</v>
       </c>
       <c r="B284" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C284">
-        <v>10</v>
+        <v>418</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
       </c>
       <c r="B285" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C285">
-        <v>11</v>
+        <v>439</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s4.1e7dc28.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
       </c>
       <c r="B286" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C286">
-        <v>12</v>
+        <v>440</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B287" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C287">
-        <v>20</v>
+        <v>446</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheRidersRanch.2035096.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
       </c>
       <c r="B288" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C288">
-        <v>28</v>
+        <v>453</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CastelBar&amp;Grill.1f72ad2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
       </c>
       <c r="B289" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C289">
-        <v>36</v>
+        <v>462</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheMarksmanBar&amp;Grill.0af1692.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B290" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C290">
-        <v>44</v>
+        <v>475</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/PitStopBar&amp;Grill.d7a6bea.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/acc.21e7f6a.webp</v>
       </c>
       <c r="B291" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C291">
-        <v>53</v>
+        <v>476</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/FamilyDining.7a275ef.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Lake%20View.8450a33.jpg</v>
       </c>
       <c r="B292" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C292">
-        <v>62</v>
+        <v>477</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ArcheryCallenge.4956286.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
       </c>
       <c r="B293" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C293">
-        <v>69</v>
+        <v>481</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.82d1f76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
       </c>
       <c r="B294" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C294">
-        <v>79</v>
+        <v>482</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeFront.55a2ad2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
       </c>
       <c r="B295" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C295">
-        <v>80</v>
+        <v>502</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Lequanda.9dcb7ac.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B296" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C296">
-        <v>81</v>
+        <v>509</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkCabanas.00f0dde.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.f4dec86.webp</v>
       </c>
       <c r="B297" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C297">
-        <v>82</v>
+        <v>519</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkDiner.e837424.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
       </c>
       <c r="B298" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C298">
-        <v>83</v>
+        <v>520</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Cabbana.911be42.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2Long.e5c90e2.webp</v>
       </c>
       <c r="B299" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C299">
-        <v>84</v>
+        <v>538</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeFrontF.37dd2a9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1Long.0f24bb8.webp</v>
       </c>
       <c r="B300" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C300">
-        <v>91</v>
+        <v>539</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CabbanaF.295b550.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B301" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C301">
-        <v>99</v>
+        <v>545</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LequandaF.73439a0.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
       </c>
       <c r="B302" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C302">
-        <v>106</v>
+        <v>554</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkDinerF.f8a74fa.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
       </c>
       <c r="B303" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C303">
-        <v>114</v>
+        <v>563</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaterparkCabanasO.a6a031a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
       </c>
       <c r="B304" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C304">
-        <v>124</v>
+        <v>580</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffetO.ea5b225.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
       </c>
       <c r="B305" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C305">
-        <v>132</v>
+        <v>581</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.89ba262.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
       </c>
       <c r="B306" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C306">
-        <v>142</v>
+        <v>587</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
       </c>
       <c r="B307" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C307">
-        <v>143</v>
+        <v>596</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.7c07513.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/prem1.ac33bc2.webp</v>
       </c>
       <c r="B308" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C308">
-        <v>144</v>
+        <v>608</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.a30d654.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/prem3.9946e8a.webp</v>
       </c>
       <c r="B309" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C309">
-        <v>145</v>
+        <v>609</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.7c07513.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/prem2.37ca344.webp</v>
       </c>
       <c r="B310" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C310">
-        <v>152</v>
+        <v>610</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long1.d4959d9.webp</v>
       </c>
       <c r="B311" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C311">
-        <v>161</v>
+        <v>617</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.89ba262.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.2c20677.webp</v>
       </c>
       <c r="B312" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C312">
-        <v>167</v>
+        <v>618</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.a30d654.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
       </c>
       <c r="B313" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C313">
-        <v>174</v>
+        <v>638</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
       </c>
       <c r="B314" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C314">
-        <v>184</v>
+        <v>646</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ThePoolBar&amp;Grill.33fc8c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
       </c>
       <c r="B315" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C315">
-        <v>185</v>
+        <v>654</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/din1.79ddaae.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun2.c4d959a.webp</v>
       </c>
       <c r="B316" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C316">
-        <v>186</v>
+        <v>664</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/din2.2a7cebb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun4.d5ce7f3.webp</v>
       </c>
       <c r="B317" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C317">
-        <v>187</v>
+        <v>665</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/din3.10849d7.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun3.ac33bc2.webp</v>
       </c>
       <c r="B318" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C318">
-        <v>188</v>
+        <v>666</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheFallsRestaurant&amp;Bar.69968c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/jun1.6e87593.webp</v>
       </c>
       <c r="B319" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C319">
-        <v>196</v>
+        <v>667</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ThePoolBar&amp;Grill.33fc8c3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.939d932.webp</v>
       </c>
       <c r="B320" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C320">
-        <v>204</v>
+        <v>687</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide.d5ccc8b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.362c90f.webp</v>
       </c>
       <c r="B321" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C321">
-        <v>216</v>
+        <v>688</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide2.ca27dc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
       </c>
       <c r="B322" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C322">
-        <v>217</v>
+        <v>694</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide3.7e0fcf3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
       </c>
       <c r="B323" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C323">
-        <v>218</v>
+        <v>701</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide4.8b1e6bb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
       </c>
       <c r="B324" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C324">
-        <v>219</v>
+        <v>708</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide5.e0dfde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Executive.56a6110.webp</v>
       </c>
       <c r="B325" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C325">
-        <v>220</v>
+        <v>718</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/dinslide6.d93b9ac.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/RIH03650.7e26c7e.webp</v>
       </c>
       <c r="B326" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C326">
-        <v>221</v>
+        <v>719</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Plaza.a45b650.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.056bfc0.webp</v>
       </c>
       <c r="B327" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C327">
-        <v>228</v>
+        <v>739</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/KuriftuBuffet.ed0beaf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.a79d619.webp</v>
       </c>
       <c r="B328" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C328">
-        <v>237</v>
+        <v>740</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TreatByThePorch.df2143d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
       </c>
       <c r="B329" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C329">
-        <v>243</v>
+        <v>746</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ReserveATable.b368639.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
       </c>
       <c r="B330" t="str">
-        <v>src/MockData/dining.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C330">
-        <v>249</v>
+        <v>753</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/contact.2e8edc6.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
       </c>
       <c r="B331" t="str">
-        <v>src/MockData/contactUsData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C331">
-        <v>2</v>
+        <v>760</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>/images/contact.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre2.7f3adf1.webp</v>
       </c>
       <c r="B332" t="str">
-        <v>src/MockData/contactUsData.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C332">
-        <v>3</v>
+        <v>770</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s5.52f7de0.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre1.43b4f0d.webp</v>
       </c>
       <c r="B333" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C333">
-        <v>10</v>
+        <v>771</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre5.c47cb91.webp</v>
       </c>
       <c r="B334" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C334">
-        <v>11</v>
+        <v>772</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s1.84eb715.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pre3.e77e1ff.webp</v>
       </c>
       <c r="B335" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C335">
-        <v>12</v>
+        <v>773</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/s2.147bc76.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long.f2c0a75.webp</v>
       </c>
       <c r="B336" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C336">
-        <v>13</v>
+        <v>793</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>/entoto/5.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/long2.47e592b.webp</v>
       </c>
       <c r="B337" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C337">
-        <v>20</v>
+        <v>794</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/re.0af1692.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
       </c>
       <c r="B338" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C338">
-        <v>29</v>
+        <v>800</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/conf.5532829.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
       </c>
       <c r="B339" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C339">
-        <v>39</v>
+        <v>807</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/MultiPurposeCabin.8dde207.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
       </c>
       <c r="B340" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/accomdations.tsx</v>
       </c>
       <c r="C340">
-        <v>50</v>
+        <v>814</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/EntotoPeakRestaurant.54d7809.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/IMG-20210910-WA0004.5ca1b87.jpg</v>
       </c>
       <c r="B341" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C341">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/TheRidersRanch.2035096.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/aboutusafrica.c7a6efc.jpg</v>
       </c>
       <c r="B342" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C342">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CastelBar&amp;Grill.1f72ad2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/pic2.16ba64d.jpg</v>
       </c>
       <c r="B343" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C343">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.5e64bc6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/p2.8eb6b5f.jpg</v>
       </c>
       <c r="B344" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C344">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SpaceOrganization.d5320f2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
       </c>
       <c r="B345" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/MockData/aboutUsPageData.tsx</v>
       </c>
       <c r="C345">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ClosingEvent.dee1570.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B346" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C346">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B347" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C347">
-        <v>111</v>
+        <v>6</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B348" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C348">
-        <v>112</v>
+        <v>7</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.0cf4a1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B349" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C349">
-        <v>113</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.a740033.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B350" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C350">
-        <v>114</v>
+        <v>49</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/birthdays.cdc6403.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B351" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C351">
-        <v>115</v>
+        <v>49</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/waterpark.9066e15.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B352" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C352">
-        <v>116</v>
+        <v>59</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1F.2b483af.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B353" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C353">
-        <v>124</v>
+        <v>60</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2F.571751b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B354" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C354">
-        <v>135</v>
+        <v>61</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3F.c2b11a7.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B355" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C355">
-        <v>146</v>
+        <v>62</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.f82bde1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B356" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C356">
-        <v>156</v>
+        <v>63</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B357" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C357">
-        <v>163</v>
+        <v>64</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.0cf4a1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B358" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C358">
-        <v>170</v>
+        <v>75</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.a54c78e.webp</v>
+        <v>https://example.com/images/boston-day-spa-1.jpg</v>
       </c>
       <c r="B359" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C359">
-        <v>177</v>
+        <v>94</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/catering.9294532.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B360" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C360">
-        <v>185</v>
+        <v>105</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1O.5433205.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B361" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C361">
-        <v>192</v>
+        <v>105</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2O.754ae7c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/go.8dde4b1.webp</v>
       </c>
       <c r="B362" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C362">
-        <v>199</v>
+        <v>118</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B363" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C363">
-        <v>212</v>
+        <v>148</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B364" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C364">
-        <v>213</v>
+        <v>148</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateRetreat.3b7233d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B365" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C365">
-        <v>214</v>
+        <v>151</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B366" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C366">
-        <v>222</v>
+        <v>152</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B367" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C367">
-        <v>233</v>
+        <v>153</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateRetreat.3b7233d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B368" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C368">
-        <v>244</v>
+        <v>154</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B369" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C369">
-        <v>254</v>
+        <v>155</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.bf76cc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B370" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C370">
-        <v>262</v>
+        <v>156</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/CorporateMembership.027accb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B371" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C371">
-        <v>270</v>
+        <v>157</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ConferenceHall.f84c697.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B372" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C372">
-        <v>278</v>
+        <v>158</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/co.e67c272.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B373" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C373">
-        <v>291</v>
+        <v>159</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/co2.c47cb91.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B374" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C374">
-        <v>292</v>
+        <v>160</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Co3.931a172.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B375" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C375">
-        <v>299</v>
+        <v>161</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/co2.c47cb91.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B376" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C376">
-        <v>309</v>
+        <v>162</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/co.e67c272.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B377" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C377">
-        <v>319</v>
+        <v>163</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Menu&amp;Catering.1e370ba.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B378" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C378">
-        <v>330</v>
+        <v>169</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SpaceOrganization.4284dbb.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B379" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C379">
-        <v>338</v>
+        <v>174</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ClosingEvent.1e10bb5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B380" t="str">
-        <v>src/MockData/celebrationsAndEvent.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C380">
-        <v>345</v>
+        <v>179</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ArtGallery.cb59c6c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/gallery2.e8d5a67.webp</v>
       </c>
       <c r="B381" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C381">
-        <v>13</v>
+        <v>187</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>/spa/spa2.JPG</v>
+        <v>https://example.com/images/kuriftu-awash-1.jpg</v>
       </c>
       <c r="B382" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C382">
-        <v>28</v>
+        <v>193</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/SteamSaunaJaccuzi.644ea57.webp</v>
+        <v>https://example.com/images/kuriftu-awash-2.jpg</v>
       </c>
       <c r="B383" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C383">
-        <v>34</v>
+        <v>194</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Massage.ce5f64d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B384" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C384">
-        <v>40</v>
+        <v>204</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B385" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C385">
-        <v>56</v>
+        <v>204</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/WaxLong.cb4bf93.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B386" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C386">
-        <v>62</v>
+        <v>207</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/ManiPediLong.e819bca.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B387" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C387">
-        <v>68</v>
+        <v>208</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Massage.ce5f64d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B388" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C388">
-        <v>80</v>
+        <v>209</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/hair.96d890e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B389" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C389">
-        <v>86</v>
+        <v>210</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Barber.4bc1f30.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B390" t="str">
-        <v>src/MockData/bostonHomeData.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C390">
-        <v>92</v>
+        <v>211</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/AfricaRoomBed.28e54c2.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B391" t="str">
-        <v>src/MockData/africanVillageAccomodation.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C391">
-        <v>30</v>
+        <v>212</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/AfricaRestaurant.36863f2.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B392" t="str">
-        <v>src/MockData/africanVillageAccomodation.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C392">
-        <v>40</v>
+        <v>213</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/AfricaMassage.ff8ac7b.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B393" t="str">
-        <v>src/MockData/africanVillageAccomodation.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C393">
-        <v>49</v>
+        <v>214</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2bb9fd7.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B394" t="str">
-        <v>src/MockData/adventure.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C394">
-        <v>9</v>
+        <v>215</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.609dbb9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B395" t="str">
-        <v>src/MockData/adventure.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C395">
-        <v>10</v>
+        <v>216</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.89f1f99.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B396" t="str">
-        <v>src/MockData/adventure.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C396">
-        <v>11</v>
+        <v>217</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/hors.1e1048c.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B397" t="str">
-        <v>src/MockData/adventure.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C397">
-        <v>19</v>
+        <v>218</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/zip.c6c6a45.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B398" t="str">
-        <v>src/MockData/adventure.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C398">
-        <v>26</v>
+        <v>219</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/play.54f31e5.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B399" t="str">
-        <v>src/MockData/adventure.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C399">
-        <v>33</v>
+        <v>225</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B400" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C400">
-        <v>11</v>
+        <v>230</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B401" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C401">
-        <v>20</v>
+        <v>235</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
+        <v>https://example.com/images/kuriftu-bishoftu.jpg</v>
       </c>
       <c r="B402" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C402">
-        <v>36</v>
+        <v>243</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
+        <v>https://example.com/images/kuriftu-bishoftu-1.jpg</v>
       </c>
       <c r="B403" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C403">
-        <v>45</v>
+        <v>249</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.1424c84.webp</v>
+        <v>https://example.com/images/kuriftu-bishoftu-2.jpg</v>
       </c>
       <c r="B404" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C404">
-        <v>54</v>
+        <v>250</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.5c6074e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B405" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C405">
-        <v>64</v>
+        <v>260</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B406" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C406">
-        <v>81</v>
+        <v>260</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B407" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C407">
-        <v>90</v>
+        <v>263</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B408" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C408">
-        <v>99</v>
+        <v>264</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Premium.eb88e0f.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B409" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C409">
-        <v>116</v>
+        <v>265</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Junior.d5ce7f3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B410" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C410">
-        <v>125</v>
+        <v>266</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Experience.56a6110.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B411" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C411">
-        <v>134</v>
+        <v>267</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.7f3adf1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B412" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C412">
-        <v>143</v>
+        <v>268</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B413" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C413">
-        <v>160</v>
+        <v>269</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/5.1d56014.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B414" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C414">
-        <v>161</v>
+        <v>270</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B415" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C415">
-        <v>181</v>
+        <v>271</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B416" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C416">
-        <v>189</v>
+        <v>272</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/slide2.2.33da435.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B417" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C417">
-        <v>190</v>
+        <v>273</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.f61845e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B418" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C418">
-        <v>199</v>
+        <v>274</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.64d69d1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B419" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C419">
-        <v>200</v>
+        <v>275</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.1ea7836.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B420" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C420">
-        <v>204</v>
+        <v>281</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.59933f3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B421" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C421">
-        <v>205</v>
+        <v>286</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.9e6f0ca.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B422" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C422">
-        <v>227</v>
+        <v>291</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0cc943d.webp</v>
+        <v>https://example.com/images/kuriftu-water-park.jpg</v>
       </c>
       <c r="B423" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C423">
-        <v>240</v>
+        <v>299</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.b0c6e49.webp</v>
+        <v>https://example.com/images/kuriftu-water-park-1.jpg</v>
       </c>
       <c r="B424" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C424">
-        <v>241</v>
+        <v>305</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.12d11d4.webp</v>
+        <v>https://example.com/images/kuriftu-water-park-2.jpg</v>
       </c>
       <c r="B425" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C425">
-        <v>242</v>
+        <v>306</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.d471ca4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B426" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C426">
-        <v>243</v>
+        <v>316</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B427" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C427">
-        <v>263</v>
+        <v>316</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B428" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C428">
-        <v>273</v>
+        <v>319</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B429" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C429">
-        <v>281</v>
+        <v>320</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.eb2af55.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B430" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C430">
-        <v>291</v>
+        <v>321</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.fcb2c4b.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B431" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C431">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.95ea902.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B432" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C432">
-        <v>293</v>
+        <v>323</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.12d11d4.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B433" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C433">
-        <v>294</v>
+        <v>324</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/gardenLong.f325f95.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B434" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C434">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/gardenLong2.a5ba8bc.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B435" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C435">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B436" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C436">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B437" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C437">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B438" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C438">
-        <v>340</v>
+        <v>329</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.0052dfd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B439" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C439">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.2faa8da.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B440" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C440">
-        <v>351</v>
+        <v>331</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.8096683.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B441" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C441">
-        <v>352</v>
+        <v>337</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.0a26366.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B442" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C442">
-        <v>353</v>
+        <v>342</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long1.f233b2e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B443" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C443">
-        <v>374</v>
+        <v>347</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.d8e3c85.webp</v>
+        <v>https://example.com/images/kuriftu-lake-tana.jpg</v>
       </c>
       <c r="B444" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C444">
-        <v>375</v>
+        <v>355</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
+        <v>https://example.com/images/kuriftu-lake-tana-1.jpg</v>
       </c>
       <c r="B445" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C445">
-        <v>381</v>
+        <v>361</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
+        <v>https://example.com/images/kuriftu-lake-tana-2.jpg</v>
       </c>
       <c r="B446" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/resort.tsx</v>
       </c>
       <c r="C446">
-        <v>390</v>
+        <v>362</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre5.9263bc8.webp</v>
+        <v>https://m.media-amazon.com/images/I/717KjgwGLXL._AC_SL1300_.jpg</v>
       </c>
       <c r="B447" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C447">
-        <v>399</v>
+        <v>4</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.020c051.webp</v>
+        <v>https://m.media-amazon.com/images/I/61306vHf8+L._UF1000,1000_QL80_.jpg</v>
       </c>
       <c r="B448" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C448">
-        <v>409</v>
+        <v>5</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Presidential.5c6074e.webp</v>
+        <v>https://pisces.bbystatic.com/image2/BestBuy_US/images/products/1585/15859171_sa.jpg</v>
       </c>
       <c r="B449" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C449">
-        <v>410</v>
+        <v>7</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.65258bc.webp</v>
+        <v>https://assets.classicfm.com/2021/50/tchaikovsky-1639562612-editorial-long-form-0.jpg</v>
       </c>
       <c r="B450" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C450">
-        <v>411</v>
+        <v>8</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.6510504.webp</v>
+        <v>https://i.ytimg.com/vi/4VZaHs_YCYk/hq720.jpg</v>
       </c>
       <c r="B451" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C451">
-        <v>412</v>
+        <v>17</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
+        <v>https://m.media-amazon.com/images/I/81qaC0JI-+L._UF894,1000_QL80_.jpg</v>
       </c>
       <c r="B452" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C452">
-        <v>433</v>
+        <v>18</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
+        <v>https://www.pianorarescores.com/wp-content/uploads/2014/10/Aram-Khachaturian.jpg</v>
       </c>
       <c r="B453" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C453">
-        <v>434</v>
+        <v>20</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
+        <v>https://m.media-amazon.com/images/I/81aNPF8YXwL._SL1500_.jpg</v>
       </c>
       <c r="B454" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C454">
-        <v>440</v>
+        <v>29</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/GardenView.eb2af55.webp</v>
+        <v>https://m.media-amazon.com/images/I/81xJdy0NcBL._SL1500_.jpg</v>
       </c>
       <c r="B455" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C455">
-        <v>447</v>
+        <v>31</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LoftVillage.745a3ee.webp</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/46/Adolphe-Adam-by-Nicolas-Eustache-Maurin.jpg</v>
       </c>
       <c r="B456" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C456">
-        <v>456</v>
+        <v>32</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://m.media-amazon.com/images/I/91se4rNs9wL._SL1500_.jpg</v>
       </c>
       <c r="B457" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C457">
-        <v>469</v>
+        <v>42</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/acc.21e7f6a.webp</v>
+        <v>https://mf.b37mrtl.ru/rbthmedia/images/2020.09/original/5f4e649f15e9f932270ee462.jpg</v>
       </c>
       <c r="B458" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C458">
-        <v>470</v>
+        <v>44</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Lake%20View.8450a33.jpg</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
       </c>
       <c r="B459" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C459">
-        <v>471</v>
+        <v>60</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
       </c>
       <c r="B460" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/gallery_items.tsx</v>
       </c>
       <c r="C460">
-        <v>475</v>
+        <v>75</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
+        <v>https://kurifturesorts.com/images/rooms/deluxe_standard_king.jpg</v>
       </c>
       <c r="B461" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C461">
-        <v>476</v>
+        <v>15</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/images/rooms/village_deluxe_king.jpg</v>
       </c>
       <c r="B462" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C462">
-        <v>496</v>
+        <v>28</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://kurifturesorts.com/images/rooms/village_deluxe_twin.jpg</v>
       </c>
       <c r="B463" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C463">
-        <v>503</v>
+        <v>41</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.f4dec86.webp</v>
+        <v>https://kurifturesorts.com/images/rooms/forest_view_king.jpg</v>
       </c>
       <c r="B464" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C464">
-        <v>513</v>
+        <v>56</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/images/rooms/forest_view_twin.jpg</v>
       </c>
       <c r="B465" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C465">
-        <v>514</v>
+        <v>69</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2Long.e5c90e2.webp</v>
+        <v>https://kurifturesorts.com/images/awash/premium_suite.jpg</v>
       </c>
       <c r="B466" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C466">
-        <v>532</v>
+        <v>85</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1Long.0f24bb8.webp</v>
+        <v>https://kurifturesorts.com/images/awash/junior_suite.jpg</v>
       </c>
       <c r="B467" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C467">
-        <v>533</v>
+        <v>110</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://kurifturesorts.com/images/awash/executive_suite.jpg</v>
       </c>
       <c r="B468" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C468">
-        <v>539</v>
+        <v>135</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
+        <v>https://kurifturesorts.com/images/awash/presidential_suite.jpg</v>
       </c>
       <c r="B469" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/accommodations.tsx</v>
       </c>
       <c r="C469">
-        <v>548</v>
+        <v>160</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.21e7f6a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
       </c>
       <c r="B470" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C470">
-        <v>557</v>
+        <v>12</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong1.d92a2e9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
       </c>
       <c r="B471" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C471">
-        <v>574</v>
+        <v>13</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/preLong2.dc8dd1d.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
       </c>
       <c r="B472" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C472">
-        <v>575</v>
+        <v>17</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6d55bab.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B473" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C473">
-        <v>581</v>
+        <v>18</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.2836597.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
       </c>
       <c r="B474" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C474">
-        <v>590</v>
+        <v>19</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/prem1.ac33bc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
       </c>
       <c r="B475" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C475">
-        <v>602</v>
+        <v>20</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/prem3.9946e8a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
       </c>
       <c r="B476" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C476">
-        <v>603</v>
+        <v>21</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/prem2.37ca344.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
       </c>
       <c r="B477" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C477">
-        <v>604</v>
+        <v>22</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long1.d4959d9.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
       </c>
       <c r="B478" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C478">
-        <v>611</v>
+        <v>23</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.2c20677.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
       </c>
       <c r="B479" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C479">
-        <v>612</v>
+        <v>24</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
       </c>
       <c r="B480" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C480">
-        <v>632</v>
+        <v>25</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
       </c>
       <c r="B481" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C481">
-        <v>640</v>
+        <v>26</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
       </c>
       <c r="B482" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C482">
-        <v>648</v>
+        <v>27</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun2.c4d959a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
       </c>
       <c r="B483" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C483">
-        <v>658</v>
+        <v>28</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun4.d5ce7f3.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
       </c>
       <c r="B484" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C484">
-        <v>659</v>
+        <v>29</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun3.ac33bc2.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
       </c>
       <c r="B485" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C485">
-        <v>660</v>
+        <v>35</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/jun1.6e87593.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
       </c>
       <c r="B486" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C486">
-        <v>661</v>
+        <v>40</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.939d932.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
       </c>
       <c r="B487" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C487">
-        <v>681</v>
+        <v>45</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.362c90f.webp</v>
+        <v>https://example.com/images/kuriftu-bishoftu.jpg</v>
       </c>
       <c r="B488" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C488">
-        <v>682</v>
+        <v>53</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
+        <v>https://example.com/images/kuriftu-bishoftu-1.jpg</v>
       </c>
       <c r="B489" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C489">
-        <v>688</v>
+        <v>60</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
+        <v>https://example.com/images/kuriftu-bishoftu-2.jpg</v>
       </c>
       <c r="B490" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/Data/MockData.tsx</v>
       </c>
       <c r="C490">
-        <v>695</v>
+        <v>61</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
       </c>
       <c r="B491" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/pages/Resort/ResortHome.tsx</v>
       </c>
       <c r="C491">
-        <v>702</v>
+        <v>355</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Executive.56a6110.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
       </c>
       <c r="B492" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/pages/Resort/ResortHome.tsx</v>
       </c>
       <c r="C492">
-        <v>712</v>
+        <v>531</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/RIH03650.7e26c7e.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bis_king.f903f0a.jpg</v>
       </c>
       <c r="B493" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/pages/Booking/RoomListing.tsx</v>
       </c>
       <c r="C493">
-        <v>713</v>
+        <v>22</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.056bfc0.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bis_king_vil.ab883eb.jpg</v>
       </c>
       <c r="B494" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/pages/Booking/RoomListing.tsx</v>
       </c>
       <c r="C494">
-        <v>733</v>
+        <v>24</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.a79d619.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bis_twins.9c2d1c7.jpg</v>
       </c>
       <c r="B495" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/pages/Booking/RoomListing.tsx</v>
       </c>
       <c r="C495">
-        <v>734</v>
+        <v>26</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/2.3cec2b4.webp</v>
       </c>
       <c r="B496" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/pages/Booking/RoomListing.tsx</v>
       </c>
       <c r="C496">
-        <v>740</v>
+        <v>30</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
       </c>
       <c r="B497" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/pages/Booking/RoomListing.tsx</v>
       </c>
       <c r="C497">
-        <v>747</v>
+        <v>32</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherpres.256c9bd.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/bis_king_vil.ab883eb.jpg</v>
       </c>
       <c r="B498" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/pages/Booking/RoomListing.tsx</v>
       </c>
       <c r="C498">
-        <v>754</v>
+        <v>36</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre2.7f3adf1.webp</v>
+        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
       </c>
       <c r="B499" t="str">
-        <v>src/MockData/accomdations.tsx</v>
+        <v>src/pages/Booking/RoomListing.tsx</v>
       </c>
       <c r="C499">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre1.43b4f0d.webp</v>
-      </c>
-      <c r="B500" t="str">
-        <v>src/MockData/accomdations.tsx</v>
-      </c>
-      <c r="C500">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre5.c47cb91.webp</v>
-      </c>
-      <c r="B501" t="str">
-        <v>src/MockData/accomdations.tsx</v>
-      </c>
-      <c r="C501">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pre3.e77e1ff.webp</v>
-      </c>
-      <c r="B502" t="str">
-        <v>src/MockData/accomdations.tsx</v>
-      </c>
-      <c r="C502">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long.f2c0a75.webp</v>
-      </c>
-      <c r="B503" t="str">
-        <v>src/MockData/accomdations.tsx</v>
-      </c>
-      <c r="C503">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/long2.47e592b.webp</v>
-      </c>
-      <c r="B504" t="str">
-        <v>src/MockData/accomdations.tsx</v>
-      </c>
-      <c r="C504">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherprem.f7b00cf.webp</v>
-      </c>
-      <c r="B505" t="str">
-        <v>src/MockData/accomdations.tsx</v>
-      </c>
-      <c r="C505">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherjun.5649c4a.webp</v>
-      </c>
-      <c r="B506" t="str">
-        <v>src/MockData/accomdations.tsx</v>
-      </c>
-      <c r="C506">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/otherex.5a70da2.webp</v>
-      </c>
-      <c r="B507" t="str">
-        <v>src/MockData/accomdations.tsx</v>
-      </c>
-      <c r="C507">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/IMG-20210910-WA0004.5ca1b87.jpg</v>
-      </c>
-      <c r="B508" t="str">
-        <v>src/MockData/aboutUsPageData.tsx</v>
-      </c>
-      <c r="C508">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/aboutusafrica.c7a6efc.jpg</v>
-      </c>
-      <c r="B509" t="str">
-        <v>src/MockData/aboutUsPageData.tsx</v>
-      </c>
-      <c r="C509">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/pic2.16ba64d.jpg</v>
-      </c>
-      <c r="B510" t="str">
-        <v>src/MockData/aboutUsPageData.tsx</v>
-      </c>
-      <c r="C510">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/p2.8eb6b5f.jpg</v>
-      </c>
-      <c r="B511" t="str">
-        <v>src/MockData/aboutUsPageData.tsx</v>
-      </c>
-      <c r="C511">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bishCele.1e852b4.webp</v>
-      </c>
-      <c r="B512" t="str">
-        <v>src/MockData/aboutUsPageData.tsx</v>
-      </c>
-      <c r="C512">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="str">
-        <v>/images/landing/apeal.JPG</v>
-      </c>
-      <c r="B513" t="str">
-        <v>src/Data/static_text.tsx</v>
-      </c>
-      <c r="C513">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-49.jpg</v>
-      </c>
-      <c r="B514" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C514">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
-      </c>
-      <c r="B515" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C515">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
-      </c>
-      <c r="B516" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C516">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
-      </c>
-      <c r="B517" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C517">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
-      </c>
-      <c r="B518" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C518">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
-      </c>
-      <c r="B519" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C519">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
-      </c>
-      <c r="B520" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C520">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
-      </c>
-      <c r="B521" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C521">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-6.jpg</v>
-      </c>
-      <c r="B522" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C522">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-35.jpg</v>
-      </c>
-      <c r="B523" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C523">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-28.jpg</v>
-      </c>
-      <c r="B524" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C524">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-40.jpg</v>
-      </c>
-      <c r="B525" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C525">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-79.jpg</v>
-      </c>
-      <c r="B526" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C526">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-76.jpg</v>
-      </c>
-      <c r="B527" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C527">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-26.jpg</v>
-      </c>
-      <c r="B528" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C528">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
-      </c>
-      <c r="B529" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C529">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
-      </c>
-      <c r="B530" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C530">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
-      </c>
-      <c r="B531" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C531">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
-      </c>
-      <c r="B532" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C532">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
-      </c>
-      <c r="B533" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C533">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
-      </c>
-      <c r="B534" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C534">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-20.jpg</v>
-      </c>
-      <c r="B535" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C535">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B536" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C536">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-51.jpg</v>
-      </c>
-      <c r="B537" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C537">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-49.jpg</v>
-      </c>
-      <c r="B538" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C538">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="str">
-        <v>https://example.com/images/boston-day-spa-1.jpg</v>
-      </c>
-      <c r="B539" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C539">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-24.jpg</v>
-      </c>
-      <c r="B540" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C540">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
-      </c>
-      <c r="B541" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C541">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
-      </c>
-      <c r="B542" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C542">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7930.jpg</v>
-      </c>
-      <c r="B543" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C543">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8509.jpg</v>
-      </c>
-      <c r="B544" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C544">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC9136.jpg</v>
-      </c>
-      <c r="B545" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C545">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7935.jpg</v>
-      </c>
-      <c r="B546" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C546">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8814.jpg</v>
-      </c>
-      <c r="B547" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C547">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/go.8dde4b1.webp</v>
-      </c>
-      <c r="B548" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C548">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8532.jpg</v>
-      </c>
-      <c r="B549" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C549">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
-      </c>
-      <c r="B550" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C550">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/Entoto+Final+.mov</v>
-      </c>
-      <c r="B551" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C551">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
-      </c>
-      <c r="B552" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C552">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
-      </c>
-      <c r="B553" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C553">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
-      </c>
-      <c r="B554" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C554">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B555" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C555">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
-      </c>
-      <c r="B556" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C556">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
-      </c>
-      <c r="B557" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C557">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
-      </c>
-      <c r="B558" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C558">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
-      </c>
-      <c r="B559" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C559">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
-      </c>
-      <c r="B560" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C560">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
-      </c>
-      <c r="B561" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C561">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
-      </c>
-      <c r="B562" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C562">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
-      </c>
-      <c r="B563" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C563">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
-      </c>
-      <c r="B564" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C564">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
-      </c>
-      <c r="B565" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C565">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
-      </c>
-      <c r="B566" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C566">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
-      </c>
-      <c r="B567" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C567">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B568" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C568">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
-      </c>
-      <c r="B569" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C569">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/gallery2.e8d5a67.webp</v>
-      </c>
-      <c r="B570" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C570">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="str">
-        <v>https://example.com/images/kuriftu-awash-1.jpg</v>
-      </c>
-      <c r="B571" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C571">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="str">
-        <v>https://example.com/images/kuriftu-awash-2.jpg</v>
-      </c>
-      <c r="B572" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C572">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
-      </c>
-      <c r="B573" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C573">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
-      </c>
-      <c r="B574" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C574">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
-      </c>
-      <c r="B575" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C575">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B576" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C576">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
-      </c>
-      <c r="B577" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C577">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
-      </c>
-      <c r="B578" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C578">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
-      </c>
-      <c r="B579" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C579">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
-      </c>
-      <c r="B580" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C580">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
-      </c>
-      <c r="B581" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C581">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
-      </c>
-      <c r="B582" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C582">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
-      </c>
-      <c r="B583" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C583">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
-      </c>
-      <c r="B584" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C584">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
-      </c>
-      <c r="B585" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C585">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
-      </c>
-      <c r="B586" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C586">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
-      </c>
-      <c r="B587" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C587">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
-      </c>
-      <c r="B588" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C588">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B589" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C589">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
-      </c>
-      <c r="B590" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C590">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu.jpg</v>
-      </c>
-      <c r="B591" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C591">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu-1.jpg</v>
-      </c>
-      <c r="B592" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C592">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu-2.jpg</v>
-      </c>
-      <c r="B593" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C593">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
-      </c>
-      <c r="B594" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C594">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
-      </c>
-      <c r="B595" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C595">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
-      </c>
-      <c r="B596" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C596">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B597" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C597">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
-      </c>
-      <c r="B598" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C598">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
-      </c>
-      <c r="B599" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C599">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
-      </c>
-      <c r="B600" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C600">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
-      </c>
-      <c r="B601" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C601">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
-      </c>
-      <c r="B602" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C602">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
-      </c>
-      <c r="B603" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C603">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
-      </c>
-      <c r="B604" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C604">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
-      </c>
-      <c r="B605" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C605">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
-      </c>
-      <c r="B606" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C606">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
-      </c>
-      <c r="B607" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C607">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
-      </c>
-      <c r="B608" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C608">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
-      </c>
-      <c r="B609" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C609">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B610" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C610">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
-      </c>
-      <c r="B611" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C611">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="str">
-        <v>https://example.com/images/kuriftu-water-park.jpg</v>
-      </c>
-      <c r="B612" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C612">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="str">
-        <v>https://example.com/images/kuriftu-water-park-1.jpg</v>
-      </c>
-      <c r="B613" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C613">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="str">
-        <v>https://example.com/images/kuriftu-water-park-2.jpg</v>
-      </c>
-      <c r="B614" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C614">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
-      </c>
-      <c r="B615" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C615">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
-      </c>
-      <c r="B616" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C616">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
-      </c>
-      <c r="B617" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C617">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B618" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C618">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
-      </c>
-      <c r="B619" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C619">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
-      </c>
-      <c r="B620" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C620">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
-      </c>
-      <c r="B621" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C621">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
-      </c>
-      <c r="B622" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C622">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
-      </c>
-      <c r="B623" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C623">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
-      </c>
-      <c r="B624" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C624">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
-      </c>
-      <c r="B625" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C625">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
-      </c>
-      <c r="B626" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C626">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
-      </c>
-      <c r="B627" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C627">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
-      </c>
-      <c r="B628" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C628">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
-      </c>
-      <c r="B629" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C629">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
-      </c>
-      <c r="B630" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C630">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B631" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C631">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
-      </c>
-      <c r="B632" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C632">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="str">
-        <v>https://example.com/images/kuriftu-lake-tana.jpg</v>
-      </c>
-      <c r="B633" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C633">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="str">
-        <v>https://example.com/images/kuriftu-lake-tana-1.jpg</v>
-      </c>
-      <c r="B634" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C634">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="str">
-        <v>https://example.com/images/kuriftu-lake-tana-2.jpg</v>
-      </c>
-      <c r="B635" t="str">
-        <v>src/Data/resort.tsx</v>
-      </c>
-      <c r="C635">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="str">
-        <v>/images/horizontalCarousel/1.webp</v>
-      </c>
-      <c r="B636" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C636">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="str">
-        <v>/images/horizontalCarousel/2.webp</v>
-      </c>
-      <c r="B637" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C637">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="str">
-        <v>/images/horizontalCarousel/3.webp</v>
-      </c>
-      <c r="B638" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C638">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="str">
-        <v>/images/horizontalCarousel/4.webp</v>
-      </c>
-      <c r="B639" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C639">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="str">
-        <v>/images/horizontalCarousel/5.webp</v>
-      </c>
-      <c r="B640" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C640">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="str">
-        <v>/images/horizontalCarousel/6.webp</v>
-      </c>
-      <c r="B641" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C641">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="str">
-        <v>/images/horizontalCarousel/7.webp</v>
-      </c>
-      <c r="B642" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C642">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="str">
-        <v>/images/experience/1.webp</v>
-      </c>
-      <c r="B643" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C643">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="str">
-        <v>/images/experience/2.webp</v>
-      </c>
-      <c r="B644" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C644">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="str">
-        <v>/images/experience/3.webp</v>
-      </c>
-      <c r="B645" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C645">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="str">
-        <v>/images/experience/4.webp</v>
-      </c>
-      <c r="B646" t="str">
-        <v>src/Data/horizontalCarousel.tsx</v>
-      </c>
-      <c r="C646">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="str">
-        <v>https://m.media-amazon.com/images/I/717KjgwGLXL._AC_SL1300_.jpg</v>
-      </c>
-      <c r="B647" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C647">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="str">
-        <v>https://m.media-amazon.com/images/I/61306vHf8+L._UF1000,1000_QL80_.jpg</v>
-      </c>
-      <c r="B648" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C648">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="str">
-        <v>https://pisces.bbystatic.com/image2/BestBuy_US/images/products/1585/15859171_sa.jpg</v>
-      </c>
-      <c r="B649" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C649">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="str">
-        <v>https://assets.classicfm.com/2021/50/tchaikovsky-1639562612-editorial-long-form-0.jpg</v>
-      </c>
-      <c r="B650" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C650">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="str">
-        <v>https://i.ytimg.com/vi/4VZaHs_YCYk/hq720.jpg</v>
-      </c>
-      <c r="B651" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C651">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="str">
-        <v>https://m.media-amazon.com/images/I/81qaC0JI-+L._UF894,1000_QL80_.jpg</v>
-      </c>
-      <c r="B652" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C652">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="str">
-        <v>https://www.pianorarescores.com/wp-content/uploads/2014/10/Aram-Khachaturian.jpg</v>
-      </c>
-      <c r="B653" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C653">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="str">
-        <v>https://m.media-amazon.com/images/I/81aNPF8YXwL._SL1500_.jpg</v>
-      </c>
-      <c r="B654" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C654">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="str">
-        <v>https://m.media-amazon.com/images/I/81xJdy0NcBL._SL1500_.jpg</v>
-      </c>
-      <c r="B655" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C655">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/4/46/Adolphe-Adam-by-Nicolas-Eustache-Maurin.jpg</v>
-      </c>
-      <c r="B656" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C656">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="str">
-        <v>https://m.media-amazon.com/images/I/91se4rNs9wL._SL1500_.jpg</v>
-      </c>
-      <c r="B657" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C657">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="str">
-        <v>https://mf.b37mrtl.ru/rbthmedia/images/2020.09/original/5f4e649f15e9f932270ee462.jpg</v>
-      </c>
-      <c r="B658" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C658">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8315.jpg</v>
-      </c>
-      <c r="B659" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C659">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8532.jpg</v>
-      </c>
-      <c r="B660" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C660">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.cba8b20.webp</v>
-      </c>
-      <c r="B661" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C661">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC9173.jpg</v>
-      </c>
-      <c r="B662" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C662">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC7949.jpg</v>
-      </c>
-      <c r="B663" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C663">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/entoto/_DSC8105.jpg</v>
-      </c>
-      <c r="B664" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C664">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON%20DAY%20SPA%20_PIER%205%20STUDIOS_OCT-50.jpg</v>
-      </c>
-      <c r="B665" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C665">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-76.jpg</v>
-      </c>
-      <c r="B666" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C666">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-16.jpg</v>
-      </c>
-      <c r="B667" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C667">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/LakeView.2b96574.webp</v>
-      </c>
-      <c r="B668" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C668">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-79.jpg</v>
-      </c>
-      <c r="B669" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C669">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/object_media/resort/boston_day_spa/BOSTON+DAY+SPA+_PIER+5+STUDIOS_OCT-24.jpg</v>
-      </c>
-      <c r="B670" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C670">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/page_media/landing/BOSTON_DAY_SPA__PIER_5_STUDIOS_OCT-13.jpg</v>
-      </c>
-      <c r="B671" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C671">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/page_media/landing/IMG_9739.jpg</v>
-      </c>
-      <c r="B672" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C672">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="str">
-        <v>https://kuriftu-media-bucket.s3.us-east-1.amazonaws.com/page_media/landing/IMG_9741.jpg</v>
-      </c>
-      <c r="B673" t="str">
-        <v>src/Data/gallery_items.tsx</v>
-      </c>
-      <c r="C673">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="str">
-        <v>https://kurifturesorts.com/images/rooms/deluxe_standard_king.jpg</v>
-      </c>
-      <c r="B674" t="str">
-        <v>src/Data/accommodations.tsx</v>
-      </c>
-      <c r="C674">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="str">
-        <v>https://kurifturesorts.com/images/rooms/village_deluxe_king.jpg</v>
-      </c>
-      <c r="B675" t="str">
-        <v>src/Data/accommodations.tsx</v>
-      </c>
-      <c r="C675">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="str">
-        <v>https://kurifturesorts.com/images/rooms/village_deluxe_twin.jpg</v>
-      </c>
-      <c r="B676" t="str">
-        <v>src/Data/accommodations.tsx</v>
-      </c>
-      <c r="C676">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="str">
-        <v>https://kurifturesorts.com/images/rooms/forest_view_king.jpg</v>
-      </c>
-      <c r="B677" t="str">
-        <v>src/Data/accommodations.tsx</v>
-      </c>
-      <c r="C677">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="str">
-        <v>https://kurifturesorts.com/images/rooms/forest_view_twin.jpg</v>
-      </c>
-      <c r="B678" t="str">
-        <v>src/Data/accommodations.tsx</v>
-      </c>
-      <c r="C678">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="str">
-        <v>https://kurifturesorts.com/images/awash/premium_suite.jpg</v>
-      </c>
-      <c r="B679" t="str">
-        <v>src/Data/accommodations.tsx</v>
-      </c>
-      <c r="C679">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="str">
-        <v>https://kurifturesorts.com/images/awash/junior_suite.jpg</v>
-      </c>
-      <c r="B680" t="str">
-        <v>src/Data/accommodations.tsx</v>
-      </c>
-      <c r="C680">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="str">
-        <v>https://kurifturesorts.com/images/awash/executive_suite.jpg</v>
-      </c>
-      <c r="B681" t="str">
-        <v>src/Data/accommodations.tsx</v>
-      </c>
-      <c r="C681">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="str">
-        <v>https://kurifturesorts.com/images/awash/presidential_suite.jpg</v>
-      </c>
-      <c r="B682" t="str">
-        <v>src/Data/accommodations.tsx</v>
-      </c>
-      <c r="C682">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
-      </c>
-      <c r="B683" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C683">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
-      </c>
-      <c r="B684" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C684">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/barber.68d5290.webp</v>
-      </c>
-      <c r="B685" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C685">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B686" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C686">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Facial.2854687.webp</v>
-      </c>
-      <c r="B687" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C687">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon.e3a2306.webp</v>
-      </c>
-      <c r="B688" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C688">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Wax.59c254e.webp</v>
-      </c>
-      <c r="B689" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C689">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/1.6aae899.jpg</v>
-      </c>
-      <c r="B690" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C690">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/3.58428a8.jpg</v>
-      </c>
-      <c r="B691" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C691">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/6.e70b338.jpg</v>
-      </c>
-      <c r="B692" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C692">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/12.fb4ab8d.jpg</v>
-      </c>
-      <c r="B693" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C693">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/11.5e9cf78.jpg</v>
-      </c>
-      <c r="B694" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C694">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/13.e4fe5a9.jpg</v>
-      </c>
-      <c r="B695" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C695">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/16.e0133a8.jpg</v>
-      </c>
-      <c r="B696" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C696">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/22.c9aa940.jpg</v>
-      </c>
-      <c r="B697" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C697">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/HairSalon1.4c3bc26.webp</v>
-      </c>
-      <c r="B698" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C698">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/suana.9596bdf.webp</v>
-      </c>
-      <c r="B699" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C699">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/21.6b04da9.jpg</v>
-      </c>
-      <c r="B700" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C700">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu.jpg</v>
-      </c>
-      <c r="B701" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C701">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu-1.jpg</v>
-      </c>
-      <c r="B702" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C702">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="str">
-        <v>https://example.com/images/kuriftu-bishoftu-2.jpg</v>
-      </c>
-      <c r="B703" t="str">
-        <v>src/Data/MockData.tsx</v>
-      </c>
-      <c r="C703">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
-      </c>
-      <c r="B704" t="str">
-        <v>src/pages/Resort/ResortHome.tsx</v>
-      </c>
-      <c r="C704">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/slide6.a9663c6.webp</v>
-      </c>
-      <c r="B705" t="str">
-        <v>src/pages/Resort/ResortHome.tsx</v>
-      </c>
-      <c r="C705">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bis_king.f903f0a.jpg</v>
-      </c>
-      <c r="B706" t="str">
-        <v>src/pages/Booking/RoomListing.tsx</v>
-      </c>
-      <c r="C706">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bis_king_vil.ab883eb.jpg</v>
-      </c>
-      <c r="B707" t="str">
-        <v>src/pages/Booking/RoomListing.tsx</v>
-      </c>
-      <c r="C707">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bis_twins.9c2d1c7.jpg</v>
-      </c>
-      <c r="B708" t="str">
-        <v>src/pages/Booking/RoomListing.tsx</v>
-      </c>
-      <c r="C708">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/2.3cec2b4.webp</v>
-      </c>
-      <c r="B709" t="str">
-        <v>src/pages/Booking/RoomListing.tsx</v>
-      </c>
-      <c r="C709">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
-      </c>
-      <c r="B710" t="str">
-        <v>src/pages/Booking/RoomListing.tsx</v>
-      </c>
-      <c r="C710">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/bis_king_vil.ab883eb.jpg</v>
-      </c>
-      <c r="B711" t="str">
-        <v>src/pages/Booking/RoomListing.tsx</v>
-      </c>
-      <c r="C711">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/Glamping.a03f5c8.webp</v>
-      </c>
-      <c r="B712" t="str">
-        <v>src/pages/Booking/RoomListing.tsx</v>
-      </c>
-      <c r="C712">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/4.61f4fcb.jpg</v>
-      </c>
-      <c r="B713" t="str">
-        <v>src/Routes/Resort/ResortDetails.tsx</v>
-      </c>
-      <c r="C713">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/9.e53335f.jpg</v>
-      </c>
-      <c r="B714" t="str">
-        <v>src/Routes/Resort/ResortDetails.tsx</v>
-      </c>
-      <c r="C714">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="str">
-        <v>https://kurifturesorts.com/_nuxt/img/17.d92b745.jpg</v>
-      </c>
-      <c r="B715" t="str">
-        <v>src/Routes/Resort/ResortDetails.tsx</v>
-      </c>
-      <c r="C715">
-        <v>98</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C715"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C499"/>
   </ignoredErrors>
 </worksheet>
 </file>